--- a/Annotation/annotation_outputs/annotation_group_2.xlsx
+++ b/Annotation/annotation_outputs/annotation_group_2.xlsx
@@ -510,7 +510,7 @@
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>taxonomy_label_correct</t>
+          <t>label_correctness</t>
         </is>
       </c>
       <c r="H1" s="3" t="inlineStr">

--- a/Annotation/annotation_outputs/annotation_group_2.xlsx
+++ b/Annotation/annotation_outputs/annotation_group_2.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,8 +30,16 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -40,12 +48,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF3F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4B2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,21 +109,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -477,7 +511,7 @@
     <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>case_id</t>
@@ -524,7 +558,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="65" customHeight="1">
       <c r="A2" s="4" t="n">
         <v>4</v>
       </c>
@@ -557,40 +591,40 @@
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="n">
+    <row r="3" ht="65" customHeight="1">
+      <c r="A3" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>what is the country of orgin of the book Pride and Prejudice</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>United Kingdom|Kingdom of Great Britain|United Kingdom of Great Britain and Ireland</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00280.json</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
+      <c r="G3" s="7" t="inlineStr"/>
+      <c r="H3" s="7" t="inlineStr"/>
+      <c r="I3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="65" customHeight="1">
       <c r="A4" s="4" t="n">
         <v>20</v>
       </c>
@@ -623,40 +657,40 @@
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="n">
+    <row r="5" ht="65" customHeight="1">
+      <c r="A5" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>kings and queens of england in the 1900s</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Edward VII | George V | Edward VIII | George VI | Elizabeth II</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Edward VII|George V|George VI|Edward VIII|Victoria|Elizabeth II</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00145.json</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="65" customHeight="1">
       <c r="A6" s="4" t="n">
         <v>32</v>
       </c>
@@ -689,40 +723,40 @@
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
+    <row r="7" ht="65" customHeight="1">
+      <c r="A7" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Who is the screen writer of the movie Dora and the Lost City of Gold</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Nicholas Stoller</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Matthew Robinson|Nicholas Stoller</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00060.json</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="65" customHeight="1">
       <c r="A8" s="4" t="n">
         <v>48</v>
       </c>
@@ -755,40 +789,40 @@
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
+    <row r="9" ht="65" customHeight="1">
+      <c r="A9" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>When did The United States Soccer Federation become affiliated and a full member with FIFA</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>1914</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>1914-06-27T00:00:00Z</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00071.json</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="65" customHeight="1">
       <c r="A10" s="4" t="n">
         <v>72</v>
       </c>
@@ -821,40 +855,40 @@
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
+    <row r="11" ht="65" customHeight="1">
+      <c r="A11" s="6" t="n">
         <v>77</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>What actress played Rose in Titanic?</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Kate Winslet</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Kate Winslet|Gloria Stuart</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00251.json</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr"/>
+      <c r="I11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="65" customHeight="1">
       <c r="A12" s="4" t="n">
         <v>85</v>
       </c>
@@ -887,40 +921,40 @@
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
+    <row r="13" ht="65" customHeight="1">
+      <c r="A13" s="6" t="n">
         <v>92</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Sort the years Michael Schumacher won the Drivers' Championship by the number of races from lowest to highest. What is the number of races in the third season in this sorted list</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>1994|16|2003|1995|17</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00113.json</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14" ht="65" customHeight="1">
       <c r="A14" s="4" t="n">
         <v>104</v>
       </c>
@@ -953,41 +987,41 @@
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
+    <row r="15" ht="65" customHeight="1">
+      <c r="A15" s="6" t="n">
         <v>111</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>What is the country of origin of the The Little Prince?</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>United States of America</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>France|France (lang:en)
 United States|United States (lang:en)</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00202.json</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16">
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="65" customHeight="1">
       <c r="A16" s="4" t="n">
         <v>117</v>
       </c>
@@ -1020,40 +1054,40 @@
       <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="5" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
+    <row r="17" ht="65" customHeight="1">
+      <c r="A17" s="6" t="n">
         <v>125</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>who is mostly responsible for writing the declaration of independence</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Thomas Jefferson</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Thomas Jefferson|Timothy Matlack</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00068.json</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="65" customHeight="1">
       <c r="A18" s="4" t="n">
         <v>132</v>
       </c>
@@ -1086,40 +1120,40 @@
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
+    <row r="19" ht="65" customHeight="1">
+      <c r="A19" s="6" t="n">
         <v>137</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>where does the water come from to fill lake eyre</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Warburton River</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Diamantina River|Georgina River|Frome River|Cooper Creek|Warburton River</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00306.json</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20">
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="65" customHeight="1">
       <c r="A20" s="4" t="n">
         <v>144</v>
       </c>
@@ -1152,40 +1186,40 @@
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr"/>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
+    <row r="21" ht="65" customHeight="1">
+      <c r="A21" s="6" t="n">
         <v>152</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>who is the actor played as Sheldon Sampson/The Utopian in Tv series Jupiter's Legacy</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Josh Duhamel</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Josh Duhamel|Elena Kampouris|Leslie Bibb|Ben Daniels</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00075.json</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22">
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22" ht="65" customHeight="1">
       <c r="A22" s="4" t="n">
         <v>160</v>
       </c>
@@ -1218,40 +1252,40 @@
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
+    <row r="23" ht="65" customHeight="1">
+      <c r="A23" s="6" t="n">
         <v>165</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>what order are the percy jackson movies in</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Percy Jackson &amp; the Olympians: The Lightning Thief | Percy Jackson: Sea of Monsters</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Percy Jackson &amp; the Olympians: The Lightning Thief|1|Percy Jackson &amp; The Olympians - The Sea of Monsters|Percy Jackson &amp; The Olympians: The Sea of Monsters|2</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00406.json</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24">
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" ht="65" customHeight="1">
       <c r="A24" s="4" t="n">
         <v>172</v>
       </c>
@@ -1284,40 +1318,40 @@
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
+    <row r="25" ht="65" customHeight="1">
+      <c r="A25" s="6" t="n">
         <v>177</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>who plays david in alvin and the chipmunks</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Jason Lee</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>Jason Lee|Q4960</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00450.json</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26">
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26" ht="65" customHeight="1">
       <c r="A26" s="4" t="n">
         <v>184</v>
       </c>
@@ -1350,40 +1384,40 @@
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
+    <row r="27" ht="65" customHeight="1">
+      <c r="A27" s="6" t="n">
         <v>189</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>What is the name of the Belgian club where Włodzimierz Lubański was a member?</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>K.S.C. Lokeren Oost-Vlaanderen</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>KV Mechelen|K.S.C. Lokeren Oost-Vlaanderen|KRC Mechelen</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00308.json</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28">
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28" ht="65" customHeight="1">
       <c r="A28" s="4" t="n">
         <v>195</v>
       </c>
@@ -1419,40 +1453,40 @@
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
+    <row r="29" ht="65" customHeight="1">
+      <c r="A29" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Who was the head coach for CF Montréal soccer team from August 10, 2011 to November 3, 2012</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>Jesse Marsch</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>Nick De Santis|2011-06-28T00:00:00Z|2011-09-30T00:00:00Z|Jesse Marsch|2011-10-01T00:00:00Z|2012-11-03T00:00:00Z</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00029.json</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30">
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30" ht="65" customHeight="1">
       <c r="A30" s="4" t="n">
         <v>213</v>
       </c>
@@ -1485,40 +1519,40 @@
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="n">
+    <row r="31" ht="65" customHeight="1">
+      <c r="A31" s="6" t="n">
         <v>225</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>where is the citrus bowl held this year</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Camping World Stadium</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>Camping World Stadium|Orlando|Orange County</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00963.json</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32">
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32" ht="65" customHeight="1">
       <c r="A32" s="4" t="n">
         <v>235</v>
       </c>
@@ -1556,40 +1590,40 @@
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr"/>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="n">
+    <row r="33" ht="65" customHeight="1">
+      <c r="A33" s="6" t="n">
         <v>249</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>when did cristiano ronaldo go to manchester united</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>2003-01-01T00:00:00Z|2021-08-27T00:00:00Z</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00058.json</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr"/>
-      <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
-    </row>
-    <row r="34">
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34" ht="65" customHeight="1">
       <c r="A34" s="4" t="n">
         <v>261</v>
       </c>
@@ -1622,40 +1656,40 @@
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="n">
+    <row r="35" ht="65" customHeight="1">
+      <c r="A35" s="6" t="n">
         <v>277</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>who is the head of the department of homeland security 2017</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>Kirstjen Nielsen</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>Jeh C. Johnson|John F. Kelly|Elaine Duke|Kirstjen Nielsen</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00099.json</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36">
+      <c r="G35" s="7" t="inlineStr"/>
+      <c r="H35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36" ht="65" customHeight="1">
       <c r="A36" s="4" t="n">
         <v>285</v>
       </c>
@@ -1688,21 +1722,21 @@
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr"/>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="n">
+    <row r="37" ht="65" customHeight="1">
+      <c r="A37" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>5 cities with the highest population in europe</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>Istanbul | Moscow | London | Saint Petersburg | Berlin</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>London|London (lang:en)|8799728.0
 Madrid city|Madrid city (lang:en)|3332035.0
@@ -1711,21 +1745,21 @@
 Barcelona|Barcelona (lang:en)|1731649.0</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00361.json</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr"/>
-      <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="5" t="inlineStr"/>
-    </row>
-    <row r="38">
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38" ht="65" customHeight="1">
       <c r="A38" s="4" t="n">
         <v>10</v>
       </c>
@@ -1760,40 +1794,40 @@
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr"/>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="n">
+    <row r="39" ht="65" customHeight="1">
+      <c r="A39" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>Neymar is from?</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>Portuguese</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00156.json</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr"/>
-      <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr"/>
-    </row>
-    <row r="40">
+      <c r="G39" s="7" t="inlineStr"/>
+      <c r="H39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40" ht="65" customHeight="1">
       <c r="A40" s="4" t="n">
         <v>22</v>
       </c>
@@ -1826,40 +1860,40 @@
       <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="n">
+    <row r="41" ht="65" customHeight="1">
+      <c r="A41" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Bethlehem Steel's won how many titles in the Lamar Hunt U.S. Open Cup</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00175.json</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr"/>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
-    </row>
-    <row r="42">
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42" ht="65" customHeight="1">
       <c r="A42" s="4" t="n">
         <v>38</v>
       </c>
@@ -1893,21 +1927,21 @@
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="n">
+    <row r="43" ht="65" customHeight="1">
+      <c r="A43" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>What are the buildings (built or in construction) with a height larger than 350 meters ?</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>Burj Khalifa | Shanghai Tower | Abraj Al-Bait Clock Tower | Ping An Finance Center | Lotte World Tower | One World Trade Center | Guangzhou CTF Finance Centre | China Zun | Taipei 101 | Shanghai World Financial Center | International Commerce Centre | Wuhan Greenland Center | Central Park Tower | Lakhta Center | Landmark 81 | Changsha IFS Tower T1 | [[Petronas Towers|Petronas Tower 2]] | Zifeng Tower | Willis Tower | KK100 | Guangzhou International Finance Center | Wuhan Center | 111 West 57th Street | One Vanderbilt | Dongguan International Trade Center 1 | 432 Park Avenue | Marina 101 | Trump International Hotel and Tower | Jin Mao Tower | Princess Tower | Al Hamra Tower | Two International Finance Centre | Guiyang International Financial Center T1 | China Resources Headquarters | CITIC Plaza | 30 Hudson Yards | Empire State Building | Elite Residence | Central Plaza | Federation Tower (East Tower) | Address Boulevard | Haitian Center Tower 2 | Bank of China Tower | Bank of America Tower | St. Regis Chicago | Almas Tower | Gevora Hotel | JW Marriott Marquis Dubai Tower 1 | JW Marriott Marquis Dubai Tower 2 | Emirates Office Tower | OKO Tower – South Tower | The Marina Torch</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>Taichung Green Museumbrary|36470.0|Taichung Green Museumbrary (lang:en)
 Kami-kawabata Building|24990.0|Kami-kawabata Building (lang:en)
@@ -1916,21 +1950,21 @@
 HOUSE EPUTA|15100.0|HOUSE EPUTA (lang:en)</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00042.json</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr"/>
-      <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr"/>
-    </row>
-    <row r="44">
+      <c r="G43" s="7" t="inlineStr"/>
+      <c r="H43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44" ht="65" customHeight="1">
       <c r="A44" s="4" t="n">
         <v>50</v>
       </c>
@@ -1963,21 +1997,21 @@
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
     </row>
-    <row r="45">
-      <c r="A45" s="4" t="n">
+    <row r="45" ht="65" customHeight="1">
+      <c r="A45" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>What are the different women wrestling promotions ?</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>[[Actwres girlZ]] | Ice Ribbon | Ladies Legend Pro-Wrestling | Oz Academy | Pro Wrestling Wave | [[Sendai Girls Pro Wrestling]] | Tokyo Joshi Pro Wrestling | World Wonder Ring Stardom | [[All Japan Womens Pro-Wrestling]] | Arsion | Gaea Japan | [[JDStar|Jd]] | JWP Joshi Puroresu</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>Sendai Girls' Pro Wrestling|Sendai Girls' Pro Wrestling (lang:en)
 Dream Star Fighting Marigold|Dream Star Fighting Marigold (lang:en)
@@ -1988,21 +2022,21 @@
 World Wonder Ring Stardom|World Wonder Ring Stardom (lang:en)</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00043.json</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr"/>
-      <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
-    </row>
-    <row r="46">
+      <c r="G45" s="7" t="inlineStr"/>
+      <c r="H45" s="7" t="inlineStr"/>
+      <c r="I45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46" ht="65" customHeight="1">
       <c r="A46" s="4" t="n">
         <v>62</v>
       </c>
@@ -2035,40 +2069,40 @@
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
     </row>
-    <row r="47">
-      <c r="A47" s="4" t="n">
+    <row r="47" ht="65" customHeight="1">
+      <c r="A47" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>How many championships were won by the Chinese football club whose home stadium is the Workers ' Stadium with a seating capacity of 66,161</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/OTT_QA_dev_complex/00373.json</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr"/>
-      <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr"/>
-    </row>
-    <row r="48">
+      <c r="G47" s="7" t="inlineStr"/>
+      <c r="H47" s="7" t="inlineStr"/>
+      <c r="I47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48" ht="65" customHeight="1">
       <c r="A48" s="4" t="n">
         <v>78</v>
       </c>
@@ -2101,40 +2135,40 @@
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="n">
+    <row r="49" ht="65" customHeight="1">
+      <c r="A49" s="6" t="n">
         <v>86</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>How many games did the 2013 New York Yankees American League Wild Card team who lost more than 100 games win against their rivals</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/OTT_QA_dev_complex/00334.json</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr"/>
-    </row>
-    <row r="50">
+      <c r="G49" s="7" t="inlineStr"/>
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50" ht="65" customHeight="1">
       <c r="A50" s="4" t="n">
         <v>91</v>
       </c>
@@ -2167,40 +2201,40 @@
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="n">
+    <row r="51" ht="65" customHeight="1">
+      <c r="A51" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>How many games involving the Boston Red Sox took place at Fenway Park across the 2018 World Series, the 2013 American League Championship Series, and the 1975 American League Championship Series</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00070.json</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr"/>
-      <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="5" t="inlineStr"/>
-    </row>
-    <row r="52">
+      <c r="G51" s="7" t="inlineStr"/>
+      <c r="H51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52" ht="65" customHeight="1">
       <c r="A52" s="4" t="n">
         <v>106</v>
       </c>
@@ -2233,40 +2267,40 @@
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
     </row>
-    <row r="53">
-      <c r="A53" s="4" t="n">
+    <row r="53" ht="65" customHeight="1">
+      <c r="A53" s="6" t="n">
         <v>114</v>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>How many games played in the 1977, 1978, 2008, and 2009 National League Championship Series between the Los Angeles Dodgers and the Philadelphia Phillies had an attendance exceeding 50,000</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00088.json</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr"/>
-      <c r="H53" s="5" t="inlineStr"/>
-      <c r="I53" s="5" t="inlineStr"/>
-    </row>
-    <row r="54">
+      <c r="G53" s="7" t="inlineStr"/>
+      <c r="H53" s="7" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54" ht="65" customHeight="1">
       <c r="A54" s="4" t="n">
         <v>119</v>
       </c>
@@ -2300,40 +2334,40 @@
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
     </row>
-    <row r="55">
-      <c r="A55" s="4" t="n">
+    <row r="55" ht="65" customHeight="1">
+      <c r="A55" s="6" t="n">
         <v>126</v>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>How many games were played at Fenway Park across the 2018 World Series, the 2013 American League Championship Series, and the 1975 American League Championship Series</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00150.json</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr"/>
-      <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr"/>
-    </row>
-    <row r="56">
+      <c r="G55" s="7" t="inlineStr"/>
+      <c r="H55" s="7" t="inlineStr"/>
+      <c r="I55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56" ht="65" customHeight="1">
       <c r="A56" s="4" t="n">
         <v>131</v>
       </c>
@@ -2366,40 +2400,40 @@
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
     </row>
-    <row r="57">
-      <c r="A57" s="4" t="n">
+    <row r="57" ht="65" customHeight="1">
+      <c r="A57" s="6" t="n">
         <v>138</v>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>How many games were played by the Boston Red Sox in the 1975 American League Championship Series, the 2013 American League Championship Series, and the 2018 World Series</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00141.json</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr"/>
-      <c r="H57" s="5" t="inlineStr"/>
-      <c r="I57" s="5" t="inlineStr"/>
-    </row>
-    <row r="58">
+      <c r="G57" s="7" t="inlineStr"/>
+      <c r="H57" s="7" t="inlineStr"/>
+      <c r="I57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58" ht="65" customHeight="1">
       <c r="A58" s="4" t="n">
         <v>143</v>
       </c>
@@ -2432,21 +2466,21 @@
       <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr"/>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="n">
+    <row r="59" ht="65" customHeight="1">
+      <c r="A59" s="6" t="n">
         <v>151</v>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>Which game is an alternate reality game ?</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>[[Ongs Hat]] | [[Majestic (video game)|Majestic]] | [[The Beast (game)|The Beast]] | ReGenesis Extended Reality | I Love Bees | Perplex City | Nowheremen | The Lost Ring | Commander Video | Superstruct | This Is My Milwaukee | [[Xi (alternate reality game)|Xi]] | Picture the Impossible | Potato Sack | Frog Fractions 2 | Cipher Hunt | Oxenfree | [[Sombra (Overwatch)|Sombra]] | [[Waking Titan (ARG)|Waking Titan]]</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>Year Zero|Year Zero (lang:en)
 Cipher Hunt|Cipher Hunt (lang:en)
@@ -2455,21 +2489,21 @@
 Adult Swim ARG|Adult Swim ARG (lang:en)</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00026.json</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr"/>
-      <c r="H59" s="5" t="inlineStr"/>
-      <c r="I59" s="5" t="inlineStr"/>
-    </row>
-    <row r="60">
+      <c r="G59" s="7" t="inlineStr"/>
+      <c r="H59" s="7" t="inlineStr"/>
+      <c r="I59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60" ht="65" customHeight="1">
       <c r="A60" s="4" t="n">
         <v>159</v>
       </c>
@@ -2502,40 +2536,40 @@
       <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr"/>
     </row>
-    <row r="61">
-      <c r="A61" s="4" t="n">
+    <row r="61" ht="65" customHeight="1">
+      <c r="A61" s="6" t="n">
         <v>166</v>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>How many gold medals were won at the 1998 Asian Games in Bangkok , Thailand by the country represented by the wrestling athlete born in Mashhad</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/OTT_QA_dev_complex/00188.json</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr"/>
-      <c r="H61" s="5" t="inlineStr"/>
-      <c r="I61" s="5" t="inlineStr"/>
-    </row>
-    <row r="62">
+      <c r="G61" s="7" t="inlineStr"/>
+      <c r="H61" s="7" t="inlineStr"/>
+      <c r="I61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62" ht="65" customHeight="1">
       <c r="A62" s="4" t="n">
         <v>175</v>
       </c>
@@ -2570,40 +2604,40 @@
       <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="inlineStr"/>
     </row>
-    <row r="63">
-      <c r="A63" s="4" t="n">
+    <row r="63" ht="65" customHeight="1">
+      <c r="A63" s="6" t="n">
         <v>182</v>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>How many matches has Jan Oblak played for Slovenia national football team in 2014</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00129.json</t>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr"/>
-      <c r="H63" s="5" t="inlineStr"/>
-      <c r="I63" s="5" t="inlineStr"/>
-    </row>
-    <row r="64">
+      <c r="G63" s="7" t="inlineStr"/>
+      <c r="H63" s="7" t="inlineStr"/>
+      <c r="I63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64" ht="65" customHeight="1">
       <c r="A64" s="4" t="n">
         <v>190</v>
       </c>
@@ -2636,40 +2670,40 @@
       <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr"/>
     </row>
-    <row r="65">
-      <c r="A65" s="4" t="n">
+    <row r="65" ht="65" customHeight="1">
+      <c r="A65" s="6" t="n">
         <v>198</v>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>How many of the teams with Victorian Football League or Australian Football League Grand Finalist history listed in the provided tables also participated in a Grand Final won by Fitzroy Football Club</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00062.json</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr"/>
-      <c r="H65" s="5" t="inlineStr"/>
-      <c r="I65" s="5" t="inlineStr"/>
-    </row>
-    <row r="66">
+      <c r="G65" s="7" t="inlineStr"/>
+      <c r="H65" s="7" t="inlineStr"/>
+      <c r="I65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66" ht="65" customHeight="1">
       <c r="A66" s="4" t="n">
         <v>203</v>
       </c>
@@ -2702,40 +2736,40 @@
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr"/>
     </row>
-    <row r="67">
-      <c r="A67" s="4" t="n">
+    <row r="67" ht="65" customHeight="1">
+      <c r="A67" s="6" t="n">
         <v>208</v>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>What is the name of the first album of the Jeff Russo</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>Lemon Parade</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>wd:Q121145482</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00236.json</t>
         </is>
       </c>
-      <c r="G67" s="5" t="inlineStr"/>
-      <c r="H67" s="5" t="inlineStr"/>
-      <c r="I67" s="5" t="inlineStr"/>
-    </row>
-    <row r="68">
+      <c r="G67" s="7" t="inlineStr"/>
+      <c r="H67" s="7" t="inlineStr"/>
+      <c r="I67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68" ht="65" customHeight="1">
       <c r="A68" s="4" t="n">
         <v>214</v>
       </c>
@@ -2768,40 +2802,40 @@
       <c r="H68" s="5" t="inlineStr"/>
       <c r="I68" s="5" t="inlineStr"/>
     </row>
-    <row r="69">
-      <c r="A69" s="4" t="n">
+    <row r="69" ht="65" customHeight="1">
+      <c r="A69" s="6" t="n">
         <v>218</v>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>How many states are served by the Air-rail alliance train company that stops at the first major airport in the New York metropolitan area</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/OTT_QA_dev_complex/00390.json</t>
         </is>
       </c>
-      <c r="G69" s="5" t="inlineStr"/>
-      <c r="H69" s="5" t="inlineStr"/>
-      <c r="I69" s="5" t="inlineStr"/>
-    </row>
-    <row r="70">
+      <c r="G69" s="7" t="inlineStr"/>
+      <c r="H69" s="7" t="inlineStr"/>
+      <c r="I69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70" ht="65" customHeight="1">
       <c r="A70" s="4" t="n">
         <v>222</v>
       </c>
@@ -2834,40 +2868,40 @@
       <c r="H70" s="5" t="inlineStr"/>
       <c r="I70" s="5" t="inlineStr"/>
     </row>
-    <row r="71">
-      <c r="A71" s="4" t="n">
+    <row r="71" ht="65" customHeight="1">
+      <c r="A71" s="6" t="n">
         <v>227</v>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>Who is the top goal scorer of the football club Borussia Dortmund?</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>Alfred Preissler</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>Manfred Burgsmüller|Manfred Burgsmüller (lang:en)|135.0</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00220.json</t>
         </is>
       </c>
-      <c r="G71" s="5" t="inlineStr"/>
-      <c r="H71" s="5" t="inlineStr"/>
-      <c r="I71" s="5" t="inlineStr"/>
-    </row>
-    <row r="72">
+      <c r="G71" s="7" t="inlineStr"/>
+      <c r="H71" s="7" t="inlineStr"/>
+      <c r="I71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72" ht="65" customHeight="1">
       <c r="A72" s="4" t="n">
         <v>231</v>
       </c>
@@ -2900,40 +2934,40 @@
       <c r="H72" s="5" t="inlineStr"/>
       <c r="I72" s="5" t="inlineStr"/>
     </row>
-    <row r="73">
-      <c r="A73" s="4" t="n">
+    <row r="73" ht="65" customHeight="1">
+      <c r="A73" s="6" t="n">
         <v>236</v>
       </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>In what year is the Most Recent Win for the VFL/AFL team ( with most pre-season cup wins between 1988–2013 ) nicknamed `` The Cats ``</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/OTT_QA_dev_complex/00220.json</t>
         </is>
       </c>
-      <c r="G73" s="5" t="inlineStr"/>
-      <c r="H73" s="5" t="inlineStr"/>
-      <c r="I73" s="5" t="inlineStr"/>
-    </row>
-    <row r="74">
+      <c r="G73" s="7" t="inlineStr"/>
+      <c r="H73" s="7" t="inlineStr"/>
+      <c r="I73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74" ht="65" customHeight="1">
       <c r="A74" s="4" t="n">
         <v>240</v>
       </c>
@@ -2966,40 +3000,40 @@
       <c r="H74" s="5" t="inlineStr"/>
       <c r="I74" s="5" t="inlineStr"/>
     </row>
-    <row r="75">
-      <c r="A75" s="4" t="n">
+    <row r="75" ht="65" customHeight="1">
+      <c r="A75" s="6" t="n">
         <v>244</v>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>In which year did the novel The Old Man and the Sea come out</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>1990</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>1952</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00132.json</t>
         </is>
       </c>
-      <c r="G75" s="5" t="inlineStr"/>
-      <c r="H75" s="5" t="inlineStr"/>
-      <c r="I75" s="5" t="inlineStr"/>
-    </row>
-    <row r="76">
+      <c r="G75" s="7" t="inlineStr"/>
+      <c r="H75" s="7" t="inlineStr"/>
+      <c r="I75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76" ht="65" customHeight="1">
       <c r="A76" s="4" t="n">
         <v>248</v>
       </c>
@@ -3032,21 +3066,21 @@
       <c r="H76" s="5" t="inlineStr"/>
       <c r="I76" s="5" t="inlineStr"/>
     </row>
-    <row r="77">
-      <c r="A77" s="4" t="n">
+    <row r="77" ht="65" customHeight="1">
+      <c r="A77" s="6" t="n">
         <v>254</v>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>How many tracks were on side two of The Police's debut album Outlandos d'Amour</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>Roxanne
 Can't Stand Losing You
@@ -3054,21 +3088,21 @@
 So Lonely</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00110.json</t>
         </is>
       </c>
-      <c r="G77" s="5" t="inlineStr"/>
-      <c r="H77" s="5" t="inlineStr"/>
-      <c r="I77" s="5" t="inlineStr"/>
-    </row>
-    <row r="78">
+      <c r="G77" s="7" t="inlineStr"/>
+      <c r="H77" s="7" t="inlineStr"/>
+      <c r="I77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78" ht="65" customHeight="1">
       <c r="A78" s="4" t="n">
         <v>258</v>
       </c>
@@ -3101,40 +3135,40 @@
       <c r="H78" s="5" t="inlineStr"/>
       <c r="I78" s="5" t="inlineStr"/>
     </row>
-    <row r="79">
-      <c r="A79" s="4" t="n">
+    <row r="79" ht="65" customHeight="1">
+      <c r="A79" s="6" t="n">
         <v>264</v>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>What is the Publication date of the second book of the novel series Little House on the Prairie</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>1 October 1993</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>1933-10-01T00:00:00Z</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00011.json</t>
         </is>
       </c>
-      <c r="G79" s="5" t="inlineStr"/>
-      <c r="H79" s="5" t="inlineStr"/>
-      <c r="I79" s="5" t="inlineStr"/>
-    </row>
-    <row r="80">
+      <c r="G79" s="7" t="inlineStr"/>
+      <c r="H79" s="7" t="inlineStr"/>
+      <c r="I79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80" ht="65" customHeight="1">
       <c r="A80" s="4" t="n">
         <v>268</v>
       </c>
@@ -3167,40 +3201,40 @@
       <c r="H80" s="5" t="inlineStr"/>
       <c r="I80" s="5" t="inlineStr"/>
     </row>
-    <row r="81">
-      <c r="A81" s="4" t="n">
+    <row r="81" ht="65" customHeight="1">
+      <c r="A81" s="6" t="n">
         <v>272</v>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>What's the US release date for the second film in the Mad Max series</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>24 December 1981</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>1982-05-21T00:00:00Z</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00128.json</t>
         </is>
       </c>
-      <c r="G81" s="5" t="inlineStr"/>
-      <c r="H81" s="5" t="inlineStr"/>
-      <c r="I81" s="5" t="inlineStr"/>
-    </row>
-    <row r="82">
+      <c r="G81" s="7" t="inlineStr"/>
+      <c r="H81" s="7" t="inlineStr"/>
+      <c r="I81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82" ht="65" customHeight="1">
       <c r="A82" s="4" t="n">
         <v>276</v>
       </c>
@@ -3233,40 +3267,40 @@
       <c r="H82" s="5" t="inlineStr"/>
       <c r="I82" s="5" t="inlineStr"/>
     </row>
-    <row r="83">
-      <c r="A83" s="4" t="n">
+    <row r="83" ht="65" customHeight="1">
+      <c r="A83" s="6" t="n">
         <v>280</v>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>When was released the song I'm Your Angel in United States in the format of Contemporary hit radio</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>13 October 1998</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>1998-11-09T00:00:00Z</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00023.json</t>
         </is>
       </c>
-      <c r="G83" s="5" t="inlineStr"/>
-      <c r="H83" s="5" t="inlineStr"/>
-      <c r="I83" s="5" t="inlineStr"/>
-    </row>
-    <row r="84">
+      <c r="G83" s="7" t="inlineStr"/>
+      <c r="H83" s="7" t="inlineStr"/>
+      <c r="I83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84" ht="65" customHeight="1">
       <c r="A84" s="4" t="n">
         <v>286</v>
       </c>
@@ -3302,40 +3336,40 @@
       <c r="H84" s="5" t="inlineStr"/>
       <c r="I84" s="5" t="inlineStr"/>
     </row>
-    <row r="85">
-      <c r="A85" s="4" t="n">
+    <row r="85" ht="65" customHeight="1">
+      <c r="A85" s="6" t="n">
         <v>292</v>
       </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>When was the B2 division club which played in Cypriot Second Division in 2013/14 , based in the second largest urban area in Cyprus founded</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>1956</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>1930</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/OTT_QA_dev_complex/00251.json</t>
         </is>
       </c>
-      <c r="G85" s="5" t="inlineStr"/>
-      <c r="H85" s="5" t="inlineStr"/>
-      <c r="I85" s="5" t="inlineStr"/>
-    </row>
-    <row r="86">
+      <c r="G85" s="7" t="inlineStr"/>
+      <c r="H85" s="7" t="inlineStr"/>
+      <c r="I85" s="7" t="inlineStr"/>
+    </row>
+    <row r="86" ht="65" customHeight="1">
       <c r="A86" s="4" t="n">
         <v>9</v>
       </c>
@@ -3368,40 +3402,40 @@
       <c r="H86" s="5" t="inlineStr"/>
       <c r="I86" s="5" t="inlineStr"/>
     </row>
-    <row r="87">
-      <c r="A87" s="4" t="n">
+    <row r="87" ht="65" customHeight="1">
+      <c r="A87" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>what is the name of the shape with 100 sides</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>hectogon | hecatontagon | hecatogon</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>hectogon</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="E87" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr">
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00482.json</t>
         </is>
       </c>
-      <c r="G87" s="5" t="inlineStr"/>
-      <c r="H87" s="5" t="inlineStr"/>
-      <c r="I87" s="5" t="inlineStr"/>
-    </row>
-    <row r="88">
+      <c r="G87" s="7" t="inlineStr"/>
+      <c r="H87" s="7" t="inlineStr"/>
+      <c r="I87" s="7" t="inlineStr"/>
+    </row>
+    <row r="88" ht="65" customHeight="1">
       <c r="A88" s="4" t="n">
         <v>49</v>
       </c>
@@ -3434,40 +3468,40 @@
       <c r="H88" s="5" t="inlineStr"/>
       <c r="I88" s="5" t="inlineStr"/>
     </row>
-    <row r="89">
-      <c r="A89" s="4" t="n">
+    <row r="89" ht="65" customHeight="1">
+      <c r="A89" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>What is the publication date of the second book The Subtle Knife of the series His Dark Materials</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
         <is>
           <t>22 July 1997</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>1997-01-01T00:00:00Z</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F89" s="4" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00014.json</t>
         </is>
       </c>
-      <c r="G89" s="5" t="inlineStr"/>
-      <c r="H89" s="5" t="inlineStr"/>
-      <c r="I89" s="5" t="inlineStr"/>
-    </row>
-    <row r="90">
+      <c r="G89" s="7" t="inlineStr"/>
+      <c r="H89" s="7" t="inlineStr"/>
+      <c r="I89" s="7" t="inlineStr"/>
+    </row>
+    <row r="90" ht="65" customHeight="1">
       <c r="A90" s="4" t="n">
         <v>68</v>
       </c>
@@ -3500,40 +3534,40 @@
       <c r="H90" s="5" t="inlineStr"/>
       <c r="I90" s="5" t="inlineStr"/>
     </row>
-    <row r="91">
-      <c r="A91" s="4" t="n">
+    <row r="91" ht="65" customHeight="1">
+      <c r="A91" s="6" t="n">
         <v>93</v>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>when did the song things that make you go hmmm come out</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>June 23, 1991</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>1991-01-01T00:00:00Z</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="E91" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00382.json</t>
         </is>
       </c>
-      <c r="G91" s="5" t="inlineStr"/>
-      <c r="H91" s="5" t="inlineStr"/>
-      <c r="I91" s="5" t="inlineStr"/>
-    </row>
-    <row r="92">
+      <c r="G91" s="7" t="inlineStr"/>
+      <c r="H91" s="7" t="inlineStr"/>
+      <c r="I91" s="7" t="inlineStr"/>
+    </row>
+    <row r="92" ht="65" customHeight="1">
       <c r="A92" s="4" t="n">
         <v>105</v>
       </c>
@@ -3566,40 +3600,40 @@
       <c r="H92" s="5" t="inlineStr"/>
       <c r="I92" s="5" t="inlineStr"/>
     </row>
-    <row r="93">
-      <c r="A93" s="4" t="n">
+    <row r="93" ht="65" customHeight="1">
+      <c r="A93" s="6" t="n">
         <v>145</v>
       </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>who wrote the song mary had a little lamb</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>Sarah Josepha Hale | John Roulstone</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="D93" s="6" t="inlineStr">
         <is>
           <t>Sarah Josepha Hale</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="E93" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F93" s="4" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00797.json</t>
         </is>
       </c>
-      <c r="G93" s="5" t="inlineStr"/>
-      <c r="H93" s="5" t="inlineStr"/>
-      <c r="I93" s="5" t="inlineStr"/>
-    </row>
-    <row r="94">
+      <c r="G93" s="7" t="inlineStr"/>
+      <c r="H93" s="7" t="inlineStr"/>
+      <c r="I93" s="7" t="inlineStr"/>
+    </row>
+    <row r="94" ht="65" customHeight="1">
       <c r="A94" s="4" t="n">
         <v>155</v>
       </c>
@@ -3632,40 +3666,40 @@
       <c r="H94" s="5" t="inlineStr"/>
       <c r="I94" s="5" t="inlineStr"/>
     </row>
-    <row r="95">
-      <c r="A95" s="4" t="n">
+    <row r="95" ht="65" customHeight="1">
+      <c r="A95" s="6" t="n">
         <v>201</v>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>who won the mens figure skating in 2018 olympics</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
         <is>
           <t>Yuzuru Hanyu | Shoma Uno | Javier Fernández</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
+      <c r="D95" s="6" t="inlineStr">
         <is>
           <t>Yuzuru Hanyū</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="E95" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F95" s="4" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00362.json</t>
         </is>
       </c>
-      <c r="G95" s="5" t="inlineStr"/>
-      <c r="H95" s="5" t="inlineStr"/>
-      <c r="I95" s="5" t="inlineStr"/>
-    </row>
-    <row r="96">
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="7" t="inlineStr"/>
+    </row>
+    <row r="96" ht="65" customHeight="1">
       <c r="A96" s="4" t="n">
         <v>223</v>
       </c>
@@ -3698,36 +3732,36 @@
       <c r="H96" s="5" t="inlineStr"/>
       <c r="I96" s="5" t="inlineStr"/>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="n">
+    <row r="97" ht="65" customHeight="1">
+      <c r="A97" s="6" t="n">
         <v>262</v>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>How many years passed between the first and last National League Championship Series featuring both the Los Angeles Dodgers and the Philadelphia Phillies</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr"/>
-      <c r="E97" s="4" t="inlineStr">
+      <c r="D97" s="6" t="inlineStr"/>
+      <c r="E97" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00198.json</t>
         </is>
       </c>
-      <c r="G97" s="5" t="inlineStr"/>
-      <c r="H97" s="5" t="inlineStr"/>
-      <c r="I97" s="5" t="inlineStr"/>
-    </row>
-    <row r="98">
+      <c r="G97" s="7" t="inlineStr"/>
+      <c r="H97" s="7" t="inlineStr"/>
+      <c r="I97" s="7" t="inlineStr"/>
+    </row>
+    <row r="98" ht="65" customHeight="1">
       <c r="A98" s="4" t="n">
         <v>287</v>
       </c>
@@ -3756,21 +3790,21 @@
       <c r="H98" s="5" t="inlineStr"/>
       <c r="I98" s="5" t="inlineStr"/>
     </row>
-    <row r="99">
-      <c r="A99" s="4" t="n">
+    <row r="99" ht="65" customHeight="1">
+      <c r="A99" s="6" t="n">
         <v>294</v>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>Listed by date of Theatrical release, chronologically, what are Neil Simon's plays which have also been made into movies</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C99" s="6" t="inlineStr">
         <is>
           <t>['Come Blow Your Horn (1961)', 'Barefoot in the Park (1963)', 'The Odd Couple (1965)', 'Sweet Charity (1966)', 'The Star-Spangled Girl (1966)', 'Plaza Suite (1968)', 'Last of the Red Hot Lovers (1969)', 'The Gingerbread Lady (1970)', 'The Sunshine Boys (1972)', 'The Prisoner of Second Avenue (1971)', 'California Suite (1976)', 'Chapter Two (1977)', 'I Ought to Be in Pictures (1980)', 'Brighton Beach Memoirs (1983)', 'Biloxi Blues (1985)', 'Broadway Bound (1986)', 'Lost in Yonkers (1991)', "Jake's Women (1992)", 'Laughter on the 23rd Floor (1993)', 'London Suite (1995)']</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="D99" s="6" t="inlineStr">
         <is>
           <t>Come Blow Your Horn|Come Blow Your Horn (lang:en)|Come Blow Your Horn|Come Blow Your Horn (lang:en)|1963-01-01T00:00:00Z
 The Odd Couple|The Odd Couple (lang:en)|The Odd Couple|The Odd Couple (lang:en)|1968-01-01T00:00:00Z
@@ -3783,21 +3817,21 @@
 Lost in Yonkers|Lost in Yonkers (lang:en)|Lost in Yonkers|Lost in Yonkers (lang:en)|1993-05-14T00:00:00Z</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
+      <c r="E99" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F99" s="4" t="inlineStr">
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Monaco_non_time_complex/00057.json</t>
         </is>
       </c>
-      <c r="G99" s="5" t="inlineStr"/>
-      <c r="H99" s="5" t="inlineStr"/>
-      <c r="I99" s="5" t="inlineStr"/>
-    </row>
-    <row r="100">
+      <c r="G99" s="7" t="inlineStr"/>
+      <c r="H99" s="7" t="inlineStr"/>
+      <c r="I99" s="7" t="inlineStr"/>
+    </row>
+    <row r="100" ht="65" customHeight="1">
       <c r="A100" s="4" t="n">
         <v>174</v>
       </c>

--- a/Annotation/annotation_outputs/annotation_group_2.xlsx
+++ b/Annotation/annotation_outputs/annotation_group_2.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$I$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -507,11 +507,13 @@
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>case_id</t>
@@ -549,10 +551,20 @@
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>wikidata_cause</t>
+          <t>missing_edge</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>missing_node</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>missing_property_or_qualifier</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -590,6 +602,8 @@
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr"/>
     </row>
     <row r="3" ht="65" customHeight="1">
       <c r="A3" s="6" t="n">
@@ -623,6 +637,8 @@
       <c r="G3" s="7" t="inlineStr"/>
       <c r="H3" s="7" t="inlineStr"/>
       <c r="I3" s="7" t="inlineStr"/>
+      <c r="J3" s="7" t="inlineStr"/>
+      <c r="K3" s="7" t="inlineStr"/>
     </row>
     <row r="4" ht="65" customHeight="1">
       <c r="A4" s="4" t="n">
@@ -656,6 +672,8 @@
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="65" customHeight="1">
       <c r="A5" s="6" t="n">
@@ -689,6 +707,8 @@
       <c r="G5" s="7" t="inlineStr"/>
       <c r="H5" s="7" t="inlineStr"/>
       <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr"/>
+      <c r="K5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="65" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -722,6 +742,8 @@
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="65" customHeight="1">
       <c r="A7" s="6" t="n">
@@ -755,6 +777,8 @@
       <c r="G7" s="7" t="inlineStr"/>
       <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr"/>
+      <c r="K7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="65" customHeight="1">
       <c r="A8" s="4" t="n">
@@ -788,6 +812,8 @@
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
     </row>
     <row r="9" ht="65" customHeight="1">
       <c r="A9" s="6" t="n">
@@ -821,6 +847,8 @@
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="7" t="inlineStr"/>
       <c r="I9" s="7" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
+      <c r="K9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="65" customHeight="1">
       <c r="A10" s="4" t="n">
@@ -854,6 +882,8 @@
       <c r="G10" s="5" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
     </row>
     <row r="11" ht="65" customHeight="1">
       <c r="A11" s="6" t="n">
@@ -887,6 +917,8 @@
       <c r="G11" s="7" t="inlineStr"/>
       <c r="H11" s="7" t="inlineStr"/>
       <c r="I11" s="7" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr"/>
+      <c r="K11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="65" customHeight="1">
       <c r="A12" s="4" t="n">
@@ -920,6 +952,8 @@
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
     </row>
     <row r="13" ht="65" customHeight="1">
       <c r="A13" s="6" t="n">
@@ -953,6 +987,8 @@
       <c r="G13" s="7" t="inlineStr"/>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr"/>
+      <c r="J13" s="7" t="inlineStr"/>
+      <c r="K13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="65" customHeight="1">
       <c r="A14" s="4" t="n">
@@ -986,6 +1022,8 @@
       <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
     </row>
     <row r="15" ht="65" customHeight="1">
       <c r="A15" s="6" t="n">
@@ -1020,6 +1058,8 @@
       <c r="G15" s="7" t="inlineStr"/>
       <c r="H15" s="7" t="inlineStr"/>
       <c r="I15" s="7" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr"/>
+      <c r="K15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="65" customHeight="1">
       <c r="A16" s="4" t="n">
@@ -1053,6 +1093,8 @@
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="65" customHeight="1">
       <c r="A17" s="6" t="n">
@@ -1086,6 +1128,8 @@
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="7" t="inlineStr"/>
       <c r="I17" s="7" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr"/>
+      <c r="K17" s="7" t="inlineStr"/>
     </row>
     <row r="18" ht="65" customHeight="1">
       <c r="A18" s="4" t="n">
@@ -1119,6 +1163,8 @@
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
     </row>
     <row r="19" ht="65" customHeight="1">
       <c r="A19" s="6" t="n">
@@ -1152,6 +1198,8 @@
       <c r="G19" s="7" t="inlineStr"/>
       <c r="H19" s="7" t="inlineStr"/>
       <c r="I19" s="7" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr"/>
+      <c r="K19" s="7" t="inlineStr"/>
     </row>
     <row r="20" ht="65" customHeight="1">
       <c r="A20" s="4" t="n">
@@ -1185,6 +1233,8 @@
       <c r="G20" s="5" t="inlineStr"/>
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
     </row>
     <row r="21" ht="65" customHeight="1">
       <c r="A21" s="6" t="n">
@@ -1218,6 +1268,8 @@
       <c r="G21" s="7" t="inlineStr"/>
       <c r="H21" s="7" t="inlineStr"/>
       <c r="I21" s="7" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr"/>
+      <c r="K21" s="7" t="inlineStr"/>
     </row>
     <row r="22" ht="65" customHeight="1">
       <c r="A22" s="4" t="n">
@@ -1251,6 +1303,8 @@
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
     </row>
     <row r="23" ht="65" customHeight="1">
       <c r="A23" s="6" t="n">
@@ -1284,6 +1338,8 @@
       <c r="G23" s="7" t="inlineStr"/>
       <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr"/>
+      <c r="K23" s="7" t="inlineStr"/>
     </row>
     <row r="24" ht="65" customHeight="1">
       <c r="A24" s="4" t="n">
@@ -1317,6 +1373,8 @@
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
     </row>
     <row r="25" ht="65" customHeight="1">
       <c r="A25" s="6" t="n">
@@ -1350,6 +1408,8 @@
       <c r="G25" s="7" t="inlineStr"/>
       <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr"/>
+      <c r="J25" s="7" t="inlineStr"/>
+      <c r="K25" s="7" t="inlineStr"/>
     </row>
     <row r="26" ht="65" customHeight="1">
       <c r="A26" s="4" t="n">
@@ -1383,6 +1443,8 @@
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
     </row>
     <row r="27" ht="65" customHeight="1">
       <c r="A27" s="6" t="n">
@@ -1416,6 +1478,8 @@
       <c r="G27" s="7" t="inlineStr"/>
       <c r="H27" s="7" t="inlineStr"/>
       <c r="I27" s="7" t="inlineStr"/>
+      <c r="J27" s="7" t="inlineStr"/>
+      <c r="K27" s="7" t="inlineStr"/>
     </row>
     <row r="28" ht="65" customHeight="1">
       <c r="A28" s="4" t="n">
@@ -1452,6 +1516,8 @@
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
     </row>
     <row r="29" ht="65" customHeight="1">
       <c r="A29" s="6" t="n">
@@ -1485,6 +1551,8 @@
       <c r="G29" s="7" t="inlineStr"/>
       <c r="H29" s="7" t="inlineStr"/>
       <c r="I29" s="7" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr"/>
+      <c r="K29" s="7" t="inlineStr"/>
     </row>
     <row r="30" ht="65" customHeight="1">
       <c r="A30" s="4" t="n">
@@ -1518,6 +1586,8 @@
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
     </row>
     <row r="31" ht="65" customHeight="1">
       <c r="A31" s="6" t="n">
@@ -1551,6 +1621,8 @@
       <c r="G31" s="7" t="inlineStr"/>
       <c r="H31" s="7" t="inlineStr"/>
       <c r="I31" s="7" t="inlineStr"/>
+      <c r="J31" s="7" t="inlineStr"/>
+      <c r="K31" s="7" t="inlineStr"/>
     </row>
     <row r="32" ht="65" customHeight="1">
       <c r="A32" s="4" t="n">
@@ -1589,6 +1661,8 @@
       <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
     </row>
     <row r="33" ht="65" customHeight="1">
       <c r="A33" s="6" t="n">
@@ -1622,6 +1696,8 @@
       <c r="G33" s="7" t="inlineStr"/>
       <c r="H33" s="7" t="inlineStr"/>
       <c r="I33" s="7" t="inlineStr"/>
+      <c r="J33" s="7" t="inlineStr"/>
+      <c r="K33" s="7" t="inlineStr"/>
     </row>
     <row r="34" ht="65" customHeight="1">
       <c r="A34" s="4" t="n">
@@ -1655,6 +1731,8 @@
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr"/>
     </row>
     <row r="35" ht="65" customHeight="1">
       <c r="A35" s="6" t="n">
@@ -1688,6 +1766,8 @@
       <c r="G35" s="7" t="inlineStr"/>
       <c r="H35" s="7" t="inlineStr"/>
       <c r="I35" s="7" t="inlineStr"/>
+      <c r="J35" s="7" t="inlineStr"/>
+      <c r="K35" s="7" t="inlineStr"/>
     </row>
     <row r="36" ht="65" customHeight="1">
       <c r="A36" s="4" t="n">
@@ -1721,6 +1801,8 @@
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
     </row>
     <row r="37" ht="65" customHeight="1">
       <c r="A37" s="6" t="n">
@@ -1758,6 +1840,8 @@
       <c r="G37" s="7" t="inlineStr"/>
       <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="7" t="inlineStr"/>
+      <c r="J37" s="7" t="inlineStr"/>
+      <c r="K37" s="7" t="inlineStr"/>
     </row>
     <row r="38" ht="65" customHeight="1">
       <c r="A38" s="4" t="n">
@@ -1793,6 +1877,8 @@
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr"/>
     </row>
     <row r="39" ht="65" customHeight="1">
       <c r="A39" s="6" t="n">
@@ -1826,6 +1912,8 @@
       <c r="G39" s="7" t="inlineStr"/>
       <c r="H39" s="7" t="inlineStr"/>
       <c r="I39" s="7" t="inlineStr"/>
+      <c r="J39" s="7" t="inlineStr"/>
+      <c r="K39" s="7" t="inlineStr"/>
     </row>
     <row r="40" ht="65" customHeight="1">
       <c r="A40" s="4" t="n">
@@ -1859,6 +1947,8 @@
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr"/>
     </row>
     <row r="41" ht="65" customHeight="1">
       <c r="A41" s="6" t="n">
@@ -1892,6 +1982,8 @@
       <c r="G41" s="7" t="inlineStr"/>
       <c r="H41" s="7" t="inlineStr"/>
       <c r="I41" s="7" t="inlineStr"/>
+      <c r="J41" s="7" t="inlineStr"/>
+      <c r="K41" s="7" t="inlineStr"/>
     </row>
     <row r="42" ht="65" customHeight="1">
       <c r="A42" s="4" t="n">
@@ -1926,6 +2018,8 @@
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="inlineStr"/>
     </row>
     <row r="43" ht="65" customHeight="1">
       <c r="A43" s="6" t="n">
@@ -1963,6 +2057,8 @@
       <c r="G43" s="7" t="inlineStr"/>
       <c r="H43" s="7" t="inlineStr"/>
       <c r="I43" s="7" t="inlineStr"/>
+      <c r="J43" s="7" t="inlineStr"/>
+      <c r="K43" s="7" t="inlineStr"/>
     </row>
     <row r="44" ht="65" customHeight="1">
       <c r="A44" s="4" t="n">
@@ -1996,6 +2092,8 @@
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="5" t="inlineStr"/>
+      <c r="K44" s="5" t="inlineStr"/>
     </row>
     <row r="45" ht="65" customHeight="1">
       <c r="A45" s="6" t="n">
@@ -2035,6 +2133,8 @@
       <c r="G45" s="7" t="inlineStr"/>
       <c r="H45" s="7" t="inlineStr"/>
       <c r="I45" s="7" t="inlineStr"/>
+      <c r="J45" s="7" t="inlineStr"/>
+      <c r="K45" s="7" t="inlineStr"/>
     </row>
     <row r="46" ht="65" customHeight="1">
       <c r="A46" s="4" t="n">
@@ -2068,6 +2168,8 @@
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr"/>
     </row>
     <row r="47" ht="65" customHeight="1">
       <c r="A47" s="6" t="n">
@@ -2101,6 +2203,8 @@
       <c r="G47" s="7" t="inlineStr"/>
       <c r="H47" s="7" t="inlineStr"/>
       <c r="I47" s="7" t="inlineStr"/>
+      <c r="J47" s="7" t="inlineStr"/>
+      <c r="K47" s="7" t="inlineStr"/>
     </row>
     <row r="48" ht="65" customHeight="1">
       <c r="A48" s="4" t="n">
@@ -2134,6 +2238,8 @@
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="5" t="inlineStr"/>
+      <c r="K48" s="5" t="inlineStr"/>
     </row>
     <row r="49" ht="65" customHeight="1">
       <c r="A49" s="6" t="n">
@@ -2167,6 +2273,8 @@
       <c r="G49" s="7" t="inlineStr"/>
       <c r="H49" s="7" t="inlineStr"/>
       <c r="I49" s="7" t="inlineStr"/>
+      <c r="J49" s="7" t="inlineStr"/>
+      <c r="K49" s="7" t="inlineStr"/>
     </row>
     <row r="50" ht="65" customHeight="1">
       <c r="A50" s="4" t="n">
@@ -2200,6 +2308,8 @@
       <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
+      <c r="J50" s="5" t="inlineStr"/>
+      <c r="K50" s="5" t="inlineStr"/>
     </row>
     <row r="51" ht="65" customHeight="1">
       <c r="A51" s="6" t="n">
@@ -2233,6 +2343,8 @@
       <c r="G51" s="7" t="inlineStr"/>
       <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr"/>
+      <c r="J51" s="7" t="inlineStr"/>
+      <c r="K51" s="7" t="inlineStr"/>
     </row>
     <row r="52" ht="65" customHeight="1">
       <c r="A52" s="4" t="n">
@@ -2266,6 +2378,8 @@
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="5" t="inlineStr"/>
+      <c r="K52" s="5" t="inlineStr"/>
     </row>
     <row r="53" ht="65" customHeight="1">
       <c r="A53" s="6" t="n">
@@ -2299,6 +2413,8 @@
       <c r="G53" s="7" t="inlineStr"/>
       <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr"/>
+      <c r="J53" s="7" t="inlineStr"/>
+      <c r="K53" s="7" t="inlineStr"/>
     </row>
     <row r="54" ht="65" customHeight="1">
       <c r="A54" s="4" t="n">
@@ -2333,6 +2449,8 @@
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="5" t="inlineStr"/>
+      <c r="K54" s="5" t="inlineStr"/>
     </row>
     <row r="55" ht="65" customHeight="1">
       <c r="A55" s="6" t="n">
@@ -2366,6 +2484,8 @@
       <c r="G55" s="7" t="inlineStr"/>
       <c r="H55" s="7" t="inlineStr"/>
       <c r="I55" s="7" t="inlineStr"/>
+      <c r="J55" s="7" t="inlineStr"/>
+      <c r="K55" s="7" t="inlineStr"/>
     </row>
     <row r="56" ht="65" customHeight="1">
       <c r="A56" s="4" t="n">
@@ -2399,6 +2519,8 @@
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
+      <c r="J56" s="5" t="inlineStr"/>
+      <c r="K56" s="5" t="inlineStr"/>
     </row>
     <row r="57" ht="65" customHeight="1">
       <c r="A57" s="6" t="n">
@@ -2432,6 +2554,8 @@
       <c r="G57" s="7" t="inlineStr"/>
       <c r="H57" s="7" t="inlineStr"/>
       <c r="I57" s="7" t="inlineStr"/>
+      <c r="J57" s="7" t="inlineStr"/>
+      <c r="K57" s="7" t="inlineStr"/>
     </row>
     <row r="58" ht="65" customHeight="1">
       <c r="A58" s="4" t="n">
@@ -2465,6 +2589,8 @@
       <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr"/>
+      <c r="J58" s="5" t="inlineStr"/>
+      <c r="K58" s="5" t="inlineStr"/>
     </row>
     <row r="59" ht="65" customHeight="1">
       <c r="A59" s="6" t="n">
@@ -2502,6 +2628,8 @@
       <c r="G59" s="7" t="inlineStr"/>
       <c r="H59" s="7" t="inlineStr"/>
       <c r="I59" s="7" t="inlineStr"/>
+      <c r="J59" s="7" t="inlineStr"/>
+      <c r="K59" s="7" t="inlineStr"/>
     </row>
     <row r="60" ht="65" customHeight="1">
       <c r="A60" s="4" t="n">
@@ -2535,6 +2663,8 @@
       <c r="G60" s="5" t="inlineStr"/>
       <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr"/>
+      <c r="J60" s="5" t="inlineStr"/>
+      <c r="K60" s="5" t="inlineStr"/>
     </row>
     <row r="61" ht="65" customHeight="1">
       <c r="A61" s="6" t="n">
@@ -2568,6 +2698,8 @@
       <c r="G61" s="7" t="inlineStr"/>
       <c r="H61" s="7" t="inlineStr"/>
       <c r="I61" s="7" t="inlineStr"/>
+      <c r="J61" s="7" t="inlineStr"/>
+      <c r="K61" s="7" t="inlineStr"/>
     </row>
     <row r="62" ht="65" customHeight="1">
       <c r="A62" s="4" t="n">
@@ -2603,6 +2735,8 @@
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="inlineStr"/>
+      <c r="J62" s="5" t="inlineStr"/>
+      <c r="K62" s="5" t="inlineStr"/>
     </row>
     <row r="63" ht="65" customHeight="1">
       <c r="A63" s="6" t="n">
@@ -2636,6 +2770,8 @@
       <c r="G63" s="7" t="inlineStr"/>
       <c r="H63" s="7" t="inlineStr"/>
       <c r="I63" s="7" t="inlineStr"/>
+      <c r="J63" s="7" t="inlineStr"/>
+      <c r="K63" s="7" t="inlineStr"/>
     </row>
     <row r="64" ht="65" customHeight="1">
       <c r="A64" s="4" t="n">
@@ -2669,6 +2805,8 @@
       <c r="G64" s="5" t="inlineStr"/>
       <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr"/>
+      <c r="J64" s="5" t="inlineStr"/>
+      <c r="K64" s="5" t="inlineStr"/>
     </row>
     <row r="65" ht="65" customHeight="1">
       <c r="A65" s="6" t="n">
@@ -2702,6 +2840,8 @@
       <c r="G65" s="7" t="inlineStr"/>
       <c r="H65" s="7" t="inlineStr"/>
       <c r="I65" s="7" t="inlineStr"/>
+      <c r="J65" s="7" t="inlineStr"/>
+      <c r="K65" s="7" t="inlineStr"/>
     </row>
     <row r="66" ht="65" customHeight="1">
       <c r="A66" s="4" t="n">
@@ -2735,6 +2875,8 @@
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr"/>
+      <c r="J66" s="5" t="inlineStr"/>
+      <c r="K66" s="5" t="inlineStr"/>
     </row>
     <row r="67" ht="65" customHeight="1">
       <c r="A67" s="6" t="n">
@@ -2768,6 +2910,8 @@
       <c r="G67" s="7" t="inlineStr"/>
       <c r="H67" s="7" t="inlineStr"/>
       <c r="I67" s="7" t="inlineStr"/>
+      <c r="J67" s="7" t="inlineStr"/>
+      <c r="K67" s="7" t="inlineStr"/>
     </row>
     <row r="68" ht="65" customHeight="1">
       <c r="A68" s="4" t="n">
@@ -2801,6 +2945,8 @@
       <c r="G68" s="5" t="inlineStr"/>
       <c r="H68" s="5" t="inlineStr"/>
       <c r="I68" s="5" t="inlineStr"/>
+      <c r="J68" s="5" t="inlineStr"/>
+      <c r="K68" s="5" t="inlineStr"/>
     </row>
     <row r="69" ht="65" customHeight="1">
       <c r="A69" s="6" t="n">
@@ -2834,6 +2980,8 @@
       <c r="G69" s="7" t="inlineStr"/>
       <c r="H69" s="7" t="inlineStr"/>
       <c r="I69" s="7" t="inlineStr"/>
+      <c r="J69" s="7" t="inlineStr"/>
+      <c r="K69" s="7" t="inlineStr"/>
     </row>
     <row r="70" ht="65" customHeight="1">
       <c r="A70" s="4" t="n">
@@ -2867,6 +3015,8 @@
       <c r="G70" s="5" t="inlineStr"/>
       <c r="H70" s="5" t="inlineStr"/>
       <c r="I70" s="5" t="inlineStr"/>
+      <c r="J70" s="5" t="inlineStr"/>
+      <c r="K70" s="5" t="inlineStr"/>
     </row>
     <row r="71" ht="65" customHeight="1">
       <c r="A71" s="6" t="n">
@@ -2900,6 +3050,8 @@
       <c r="G71" s="7" t="inlineStr"/>
       <c r="H71" s="7" t="inlineStr"/>
       <c r="I71" s="7" t="inlineStr"/>
+      <c r="J71" s="7" t="inlineStr"/>
+      <c r="K71" s="7" t="inlineStr"/>
     </row>
     <row r="72" ht="65" customHeight="1">
       <c r="A72" s="4" t="n">
@@ -2933,6 +3085,8 @@
       <c r="G72" s="5" t="inlineStr"/>
       <c r="H72" s="5" t="inlineStr"/>
       <c r="I72" s="5" t="inlineStr"/>
+      <c r="J72" s="5" t="inlineStr"/>
+      <c r="K72" s="5" t="inlineStr"/>
     </row>
     <row r="73" ht="65" customHeight="1">
       <c r="A73" s="6" t="n">
@@ -2966,6 +3120,8 @@
       <c r="G73" s="7" t="inlineStr"/>
       <c r="H73" s="7" t="inlineStr"/>
       <c r="I73" s="7" t="inlineStr"/>
+      <c r="J73" s="7" t="inlineStr"/>
+      <c r="K73" s="7" t="inlineStr"/>
     </row>
     <row r="74" ht="65" customHeight="1">
       <c r="A74" s="4" t="n">
@@ -2999,6 +3155,8 @@
       <c r="G74" s="5" t="inlineStr"/>
       <c r="H74" s="5" t="inlineStr"/>
       <c r="I74" s="5" t="inlineStr"/>
+      <c r="J74" s="5" t="inlineStr"/>
+      <c r="K74" s="5" t="inlineStr"/>
     </row>
     <row r="75" ht="65" customHeight="1">
       <c r="A75" s="6" t="n">
@@ -3032,6 +3190,8 @@
       <c r="G75" s="7" t="inlineStr"/>
       <c r="H75" s="7" t="inlineStr"/>
       <c r="I75" s="7" t="inlineStr"/>
+      <c r="J75" s="7" t="inlineStr"/>
+      <c r="K75" s="7" t="inlineStr"/>
     </row>
     <row r="76" ht="65" customHeight="1">
       <c r="A76" s="4" t="n">
@@ -3065,6 +3225,8 @@
       <c r="G76" s="5" t="inlineStr"/>
       <c r="H76" s="5" t="inlineStr"/>
       <c r="I76" s="5" t="inlineStr"/>
+      <c r="J76" s="5" t="inlineStr"/>
+      <c r="K76" s="5" t="inlineStr"/>
     </row>
     <row r="77" ht="65" customHeight="1">
       <c r="A77" s="6" t="n">
@@ -3101,6 +3263,8 @@
       <c r="G77" s="7" t="inlineStr"/>
       <c r="H77" s="7" t="inlineStr"/>
       <c r="I77" s="7" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr"/>
+      <c r="K77" s="7" t="inlineStr"/>
     </row>
     <row r="78" ht="65" customHeight="1">
       <c r="A78" s="4" t="n">
@@ -3134,6 +3298,8 @@
       <c r="G78" s="5" t="inlineStr"/>
       <c r="H78" s="5" t="inlineStr"/>
       <c r="I78" s="5" t="inlineStr"/>
+      <c r="J78" s="5" t="inlineStr"/>
+      <c r="K78" s="5" t="inlineStr"/>
     </row>
     <row r="79" ht="65" customHeight="1">
       <c r="A79" s="6" t="n">
@@ -3167,6 +3333,8 @@
       <c r="G79" s="7" t="inlineStr"/>
       <c r="H79" s="7" t="inlineStr"/>
       <c r="I79" s="7" t="inlineStr"/>
+      <c r="J79" s="7" t="inlineStr"/>
+      <c r="K79" s="7" t="inlineStr"/>
     </row>
     <row r="80" ht="65" customHeight="1">
       <c r="A80" s="4" t="n">
@@ -3200,6 +3368,8 @@
       <c r="G80" s="5" t="inlineStr"/>
       <c r="H80" s="5" t="inlineStr"/>
       <c r="I80" s="5" t="inlineStr"/>
+      <c r="J80" s="5" t="inlineStr"/>
+      <c r="K80" s="5" t="inlineStr"/>
     </row>
     <row r="81" ht="65" customHeight="1">
       <c r="A81" s="6" t="n">
@@ -3233,6 +3403,8 @@
       <c r="G81" s="7" t="inlineStr"/>
       <c r="H81" s="7" t="inlineStr"/>
       <c r="I81" s="7" t="inlineStr"/>
+      <c r="J81" s="7" t="inlineStr"/>
+      <c r="K81" s="7" t="inlineStr"/>
     </row>
     <row r="82" ht="65" customHeight="1">
       <c r="A82" s="4" t="n">
@@ -3266,6 +3438,8 @@
       <c r="G82" s="5" t="inlineStr"/>
       <c r="H82" s="5" t="inlineStr"/>
       <c r="I82" s="5" t="inlineStr"/>
+      <c r="J82" s="5" t="inlineStr"/>
+      <c r="K82" s="5" t="inlineStr"/>
     </row>
     <row r="83" ht="65" customHeight="1">
       <c r="A83" s="6" t="n">
@@ -3299,6 +3473,8 @@
       <c r="G83" s="7" t="inlineStr"/>
       <c r="H83" s="7" t="inlineStr"/>
       <c r="I83" s="7" t="inlineStr"/>
+      <c r="J83" s="7" t="inlineStr"/>
+      <c r="K83" s="7" t="inlineStr"/>
     </row>
     <row r="84" ht="65" customHeight="1">
       <c r="A84" s="4" t="n">
@@ -3335,6 +3511,8 @@
       <c r="G84" s="5" t="inlineStr"/>
       <c r="H84" s="5" t="inlineStr"/>
       <c r="I84" s="5" t="inlineStr"/>
+      <c r="J84" s="5" t="inlineStr"/>
+      <c r="K84" s="5" t="inlineStr"/>
     </row>
     <row r="85" ht="65" customHeight="1">
       <c r="A85" s="6" t="n">
@@ -3368,6 +3546,8 @@
       <c r="G85" s="7" t="inlineStr"/>
       <c r="H85" s="7" t="inlineStr"/>
       <c r="I85" s="7" t="inlineStr"/>
+      <c r="J85" s="7" t="inlineStr"/>
+      <c r="K85" s="7" t="inlineStr"/>
     </row>
     <row r="86" ht="65" customHeight="1">
       <c r="A86" s="4" t="n">
@@ -3401,6 +3581,8 @@
       <c r="G86" s="5" t="inlineStr"/>
       <c r="H86" s="5" t="inlineStr"/>
       <c r="I86" s="5" t="inlineStr"/>
+      <c r="J86" s="5" t="inlineStr"/>
+      <c r="K86" s="5" t="inlineStr"/>
     </row>
     <row r="87" ht="65" customHeight="1">
       <c r="A87" s="6" t="n">
@@ -3434,6 +3616,8 @@
       <c r="G87" s="7" t="inlineStr"/>
       <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="7" t="inlineStr"/>
+      <c r="J87" s="7" t="inlineStr"/>
+      <c r="K87" s="7" t="inlineStr"/>
     </row>
     <row r="88" ht="65" customHeight="1">
       <c r="A88" s="4" t="n">
@@ -3467,6 +3651,8 @@
       <c r="G88" s="5" t="inlineStr"/>
       <c r="H88" s="5" t="inlineStr"/>
       <c r="I88" s="5" t="inlineStr"/>
+      <c r="J88" s="5" t="inlineStr"/>
+      <c r="K88" s="5" t="inlineStr"/>
     </row>
     <row r="89" ht="65" customHeight="1">
       <c r="A89" s="6" t="n">
@@ -3500,6 +3686,8 @@
       <c r="G89" s="7" t="inlineStr"/>
       <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="7" t="inlineStr"/>
+      <c r="J89" s="7" t="inlineStr"/>
+      <c r="K89" s="7" t="inlineStr"/>
     </row>
     <row r="90" ht="65" customHeight="1">
       <c r="A90" s="4" t="n">
@@ -3533,6 +3721,8 @@
       <c r="G90" s="5" t="inlineStr"/>
       <c r="H90" s="5" t="inlineStr"/>
       <c r="I90" s="5" t="inlineStr"/>
+      <c r="J90" s="5" t="inlineStr"/>
+      <c r="K90" s="5" t="inlineStr"/>
     </row>
     <row r="91" ht="65" customHeight="1">
       <c r="A91" s="6" t="n">
@@ -3566,6 +3756,8 @@
       <c r="G91" s="7" t="inlineStr"/>
       <c r="H91" s="7" t="inlineStr"/>
       <c r="I91" s="7" t="inlineStr"/>
+      <c r="J91" s="7" t="inlineStr"/>
+      <c r="K91" s="7" t="inlineStr"/>
     </row>
     <row r="92" ht="65" customHeight="1">
       <c r="A92" s="4" t="n">
@@ -3599,6 +3791,8 @@
       <c r="G92" s="5" t="inlineStr"/>
       <c r="H92" s="5" t="inlineStr"/>
       <c r="I92" s="5" t="inlineStr"/>
+      <c r="J92" s="5" t="inlineStr"/>
+      <c r="K92" s="5" t="inlineStr"/>
     </row>
     <row r="93" ht="65" customHeight="1">
       <c r="A93" s="6" t="n">
@@ -3632,6 +3826,8 @@
       <c r="G93" s="7" t="inlineStr"/>
       <c r="H93" s="7" t="inlineStr"/>
       <c r="I93" s="7" t="inlineStr"/>
+      <c r="J93" s="7" t="inlineStr"/>
+      <c r="K93" s="7" t="inlineStr"/>
     </row>
     <row r="94" ht="65" customHeight="1">
       <c r="A94" s="4" t="n">
@@ -3665,6 +3861,8 @@
       <c r="G94" s="5" t="inlineStr"/>
       <c r="H94" s="5" t="inlineStr"/>
       <c r="I94" s="5" t="inlineStr"/>
+      <c r="J94" s="5" t="inlineStr"/>
+      <c r="K94" s="5" t="inlineStr"/>
     </row>
     <row r="95" ht="65" customHeight="1">
       <c r="A95" s="6" t="n">
@@ -3698,6 +3896,8 @@
       <c r="G95" s="7" t="inlineStr"/>
       <c r="H95" s="7" t="inlineStr"/>
       <c r="I95" s="7" t="inlineStr"/>
+      <c r="J95" s="7" t="inlineStr"/>
+      <c r="K95" s="7" t="inlineStr"/>
     </row>
     <row r="96" ht="65" customHeight="1">
       <c r="A96" s="4" t="n">
@@ -3731,6 +3931,8 @@
       <c r="G96" s="5" t="inlineStr"/>
       <c r="H96" s="5" t="inlineStr"/>
       <c r="I96" s="5" t="inlineStr"/>
+      <c r="J96" s="5" t="inlineStr"/>
+      <c r="K96" s="5" t="inlineStr"/>
     </row>
     <row r="97" ht="65" customHeight="1">
       <c r="A97" s="6" t="n">
@@ -3760,6 +3962,8 @@
       <c r="G97" s="7" t="inlineStr"/>
       <c r="H97" s="7" t="inlineStr"/>
       <c r="I97" s="7" t="inlineStr"/>
+      <c r="J97" s="7" t="inlineStr"/>
+      <c r="K97" s="7" t="inlineStr"/>
     </row>
     <row r="98" ht="65" customHeight="1">
       <c r="A98" s="4" t="n">
@@ -3789,6 +3993,8 @@
       <c r="G98" s="5" t="inlineStr"/>
       <c r="H98" s="5" t="inlineStr"/>
       <c r="I98" s="5" t="inlineStr"/>
+      <c r="J98" s="5" t="inlineStr"/>
+      <c r="K98" s="5" t="inlineStr"/>
     </row>
     <row r="99" ht="65" customHeight="1">
       <c r="A99" s="6" t="n">
@@ -3830,6 +4036,8 @@
       <c r="G99" s="7" t="inlineStr"/>
       <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="7" t="inlineStr"/>
+      <c r="J99" s="7" t="inlineStr"/>
+      <c r="K99" s="7" t="inlineStr"/>
     </row>
     <row r="100" ht="65" customHeight="1">
       <c r="A100" s="4" t="n">
@@ -3863,15 +4071,17 @@
       <c r="G100" s="5" t="inlineStr"/>
       <c r="H100" s="5" t="inlineStr"/>
       <c r="I100" s="5" t="inlineStr"/>
+      <c r="J100" s="5" t="inlineStr"/>
+      <c r="K100" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I100"/>
+  <autoFilter ref="A1:K100"/>
   <dataValidations count="2">
     <dataValidation sqref="G2:G100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Correct,Incorrect,Unsure"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Missing edge,Missing node,Missing property/qualifier,Not applicable,Unsure"</formula1>
+    <dataValidation sqref="H2:H100 I2:I100 J2:J100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Annotation/annotation_outputs/annotation_group_2.xlsx
+++ b/Annotation/annotation_outputs/annotation_group_2.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$M$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -497,20 +497,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -536,35 +538,45 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>SPARQL</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Corrected SPARQL</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
           <t>taxonomy_label</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>label_correctness</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>missing_edge</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>missing_node</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>missing_property_or_qualifier</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -591,19 +603,29 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?party ?partyLabel WHERE {
+  wd:Q43203 wdt:P102 ?party .
+  ?party rdfs:label ?partyLabel .
+  FILTER(lang(?partyLabel) = 'en')
+}</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00013.json</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr"/>
       <c r="J2" s="5" t="inlineStr"/>
       <c r="K2" s="5" t="inlineStr"/>
+      <c r="L2" s="5" t="inlineStr"/>
+      <c r="M2" s="5" t="inlineStr"/>
     </row>
     <row r="3" ht="65" customHeight="1">
       <c r="A3" s="6" t="n">
@@ -626,19 +648,27 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?country WHERE {
+  wd:Q170583 wdt:P495 ?country
+}</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr"/>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00280.json</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr"/>
-      <c r="H3" s="7" t="inlineStr"/>
       <c r="I3" s="7" t="inlineStr"/>
       <c r="J3" s="7" t="inlineStr"/>
       <c r="K3" s="7" t="inlineStr"/>
+      <c r="L3" s="7" t="inlineStr"/>
+      <c r="M3" s="7" t="inlineStr"/>
     </row>
     <row r="4" ht="65" customHeight="1">
       <c r="A4" s="4" t="n">
@@ -661,19 +691,27 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?genre WHERE {
+  wd:Q184342 wdt:P136 ?genre
+}</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00255.json</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="65" customHeight="1">
       <c r="A5" s="6" t="n">
@@ -696,19 +734,38 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
+          <t>SELECT DISTINCT ?monarch ?monarchLabel WHERE {
+  ?monarch p:P39 ?statement .
+  ?statement ps:P39 ?position .
+  VALUES ?position {
+    wd:Q9134365 wd:Q111722535
+  }
+  .
+  ?statement pq:P580 ?start ; pq:P582 ?end .
+  FILTER(xsd:dateTime(?start) &lt;= "2000-12-31T23:59:59Z" ^^ xsd:dateTime &amp;&amp; xsd:dateTime(?end) &gt;= "1901-01-01T00:00:00Z" ^^ xsd:dateTime)
+  OPTIONAL {
+    ?monarch rdfs:label ?monarchLabel .
+    FILTER(lang(?monarchLabel) = "en")
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00145.json</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr"/>
       <c r="I5" s="7" t="inlineStr"/>
       <c r="J5" s="7" t="inlineStr"/>
       <c r="K5" s="7" t="inlineStr"/>
+      <c r="L5" s="7" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="65" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -731,19 +788,27 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?distributor WHERE {
+  wd:Q1198269 wdt:P750 ?distributor
+}</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00071.json</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="65" customHeight="1">
       <c r="A7" s="6" t="n">
@@ -766,19 +831,27 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?screenwriter WHERE {
+  wd:Q56064745 wdt:P58 ?screenwriter
+}</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00060.json</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="7" t="inlineStr"/>
       <c r="J7" s="7" t="inlineStr"/>
       <c r="K7" s="7" t="inlineStr"/>
+      <c r="L7" s="7" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="65" customHeight="1">
       <c r="A8" s="4" t="n">
@@ -801,19 +874,27 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?composer WHERE {
+  wd:Q56064745 wdt:P86 ?composer
+}</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00096.json</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
       <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
     </row>
     <row r="9" ht="65" customHeight="1">
       <c r="A9" s="6" t="n">
@@ -836,19 +917,29 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?date WHERE {
+  wd:Q222131 p:P463 ?statement .
+  ?statement ps:P463 wd:Q253414 .
+  ?statement pq:P580 ?date .
+}</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00071.json</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
       <c r="I9" s="7" t="inlineStr"/>
       <c r="J9" s="7" t="inlineStr"/>
       <c r="K9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="65" customHeight="1">
       <c r="A10" s="4" t="n">
@@ -871,19 +962,29 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?releaseDate WHERE {
+  wd:Q21534241 wdt:P577 ?releaseDate .
+}
+ORDER BY ?releaseDate
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00078.json</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
       <c r="J10" s="5" t="inlineStr"/>
       <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
     </row>
     <row r="11" ht="65" customHeight="1">
       <c r="A11" s="6" t="n">
@@ -906,19 +1007,29 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?actor WHERE {
+  wd:Q44578 p:P161 ?cast .
+  ?cast ps:P161 ?actor .
+  ?cast pq:P453 wd:Q4892194 .
+}</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00251.json</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr"/>
       <c r="I11" s="7" t="inlineStr"/>
       <c r="J11" s="7" t="inlineStr"/>
       <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="65" customHeight="1">
       <c r="A12" s="4" t="n">
@@ -941,19 +1052,27 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?alias WHERE {
+  wd:Q9616 wdt:P1449 ?alias
+}</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00183.json</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
       <c r="J12" s="5" t="inlineStr"/>
       <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
     </row>
     <row r="13" ht="65" customHeight="1">
       <c r="A13" s="6" t="n">
@@ -976,19 +1095,32 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?year(xsd:integer(?races) AS ?racesNum) WHERE {
+  ?season wdt:P1346 wd:Q9671 .
+  ?season wdt:P580 ?startTime .
+  ?season wdt:P1350 ?races .
+  BIND(YEAR(?startTime) AS ?year)
+}
+ORDER BY ASC(?racesNum)
+LIMIT 3</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00113.json</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr"/>
       <c r="J13" s="7" t="inlineStr"/>
       <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="65" customHeight="1">
       <c r="A14" s="4" t="n">
@@ -1011,19 +1143,41 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?movie ?movieLabel(COUNT(*) AS ?awardCount) WHERE {
+  ?movie wdt:P57 wd:Q43203 .
+  ?movie wdt:P31 / wdt:P279 * wd:Q11424 .
+  ?movie wdt:P166 ?award .
+  {
+    ?award wdt:P31 / wdt:P279 * wd:Q19020
+  } UNION {
+    ?award wdt:P31 / wdt:P279 * wd:Q1326532
+  }
+  OPTIONAL {
+    ?movie rdfs:label ?movieLabel .
+    FILTER(LANG(?movieLabel) = "en")
+  }
+}
+GROUP BY ?movie ?movieLabel
+ORDER BY DESC(?awardCount)
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00060.json</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
       <c r="J14" s="5" t="inlineStr"/>
       <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
     </row>
     <row r="15" ht="65" customHeight="1">
       <c r="A15" s="6" t="n">
@@ -1047,19 +1201,29 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
+          <t>SELECT DISTINCT ?country ?countryLabel WHERE {
+  wd:Q25338 wdt:P495 ?country .
+  ?country rdfs:label ?countryLabel .
+  FILTER(LANG(?countryLabel) = "en")
+}</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00202.json</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr"/>
       <c r="I15" s="7" t="inlineStr"/>
       <c r="J15" s="7" t="inlineStr"/>
       <c r="K15" s="7" t="inlineStr"/>
+      <c r="L15" s="7" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="65" customHeight="1">
       <c r="A16" s="4" t="n">
@@ -1082,19 +1246,31 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?actor ?label WHERE {
+  wd:Q177329 wdt:P175 ?actor .
+  OPTIONAL {
+    ?actor rdfs:label ?label
+    FILTER(LANG(?label) = "en")
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00189.json</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="5" t="inlineStr"/>
       <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="65" customHeight="1">
       <c r="A17" s="6" t="n">
@@ -1117,19 +1293,27 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?author WHERE {
+  wd:Q127912 wdt:P50 ?author .
+}</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00068.json</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="7" t="inlineStr"/>
       <c r="I17" s="7" t="inlineStr"/>
       <c r="J17" s="7" t="inlineStr"/>
       <c r="K17" s="7" t="inlineStr"/>
+      <c r="L17" s="7" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
     </row>
     <row r="18" ht="65" customHeight="1">
       <c r="A18" s="4" t="n">
@@ -1152,19 +1336,35 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
+          <t>SELECT DISTINCT ?player ?playerLabel WHERE {
+  ?player p:P166 / ps:P166 wd:Q233454 .
+  ?player p:P166 / pq:P585 ?date .
+  FILTER(YEAR(?date) = 2006)
+  .
+  OPTIONAL {
+    ?player rdfs:label ?playerLabel .
+    FILTER(LANG(?playerLabel) = "en")
+    .
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00221.json</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr"/>
       <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
     </row>
     <row r="19" ht="65" customHeight="1">
       <c r="A19" s="6" t="n">
@@ -1187,19 +1387,29 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?inflow ?inflowLabel WHERE {
+  wd:Q179970 wdt:P200 ?inflow .
+  ?inflow rdfs:label ?inflowLabel .
+  FILTER(lang(?inflowLabel) = 'en')
+}</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00306.json</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr"/>
       <c r="I19" s="7" t="inlineStr"/>
       <c r="J19" s="7" t="inlineStr"/>
       <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="7" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
     </row>
     <row r="20" ht="65" customHeight="1">
       <c r="A20" s="4" t="n">
@@ -1222,19 +1432,30 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?book ?date WHERE {
+  wd:Q18153036 wdt:P527 ?book .
+  ?book wdt:P577 ?date .
+}
+ORDER BY ASC(?date)
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00105.json</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="5" t="inlineStr"/>
       <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
     </row>
     <row r="21" ht="65" customHeight="1">
       <c r="A21" s="6" t="n">
@@ -1257,19 +1478,29 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?actor ?actorLabel WHERE {
+  wd:Q65120863 wdt:P161 ?actor .
+  ?actor rdfs:label ?actorLabel .
+  FILTER(LANG(?actorLabel) = 'en')
+}</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00075.json</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
       <c r="I21" s="7" t="inlineStr"/>
       <c r="J21" s="7" t="inlineStr"/>
       <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
     </row>
     <row r="22" ht="65" customHeight="1">
       <c r="A22" s="4" t="n">
@@ -1292,19 +1523,30 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?author ?label WHERE {
+  wd:Q326914 wdt:P50 ?author .
+  wd:Q215410 wdt:P50 ?author .
+  ?author rdfs:label ?label .
+  FILTER(LANG(?label) = "en")
+}</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00138.json</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
     </row>
     <row r="23" ht="65" customHeight="1">
       <c r="A23" s="6" t="n">
@@ -1327,19 +1569,32 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?movie ?title ?ordinal WHERE {
+  wd:Q7167417 p:P527 ?statement .
+  ?statement ps:P527 ?movie .
+  ?statement pq:P1545 ?ordinal .
+  ?movie rdfs:label ?title .
+  FILTER(LANG(?title) = "en")
+}
+ORDER BY ASC(?ordinal)</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00406.json</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="7" t="inlineStr"/>
       <c r="J23" s="7" t="inlineStr"/>
       <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
     </row>
     <row r="24" ht="65" customHeight="1">
       <c r="A24" s="4" t="n">
@@ -1362,19 +1617,30 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?directorLabel WHERE {
+  wd:Q26505 wdt:P4969 ?film .
+  ?film wdt:P57 ?director .
+  ?director rdfs:label ?directorLabel .
+  FILTER(LANG(?directorLabel) = 'en')
+}</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00299.json</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr"/>
       <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
     </row>
     <row r="25" ht="65" customHeight="1">
       <c r="A25" s="6" t="n">
@@ -1397,19 +1663,30 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?actor(STRAFTER(STR(?actor) , "http://www.wikidata.org/entity/") AS ?actor_id) ?label WHERE {
+  wd:Q26823554 wdt:P175 ?actor .
+  ?actor rdfs:label ?label .
+  FILTER(LANG(?label) = "en")
+}
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00450.json</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr"/>
       <c r="J25" s="7" t="inlineStr"/>
       <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
     </row>
     <row r="26" ht="65" customHeight="1">
       <c r="A26" s="4" t="n">
@@ -1432,19 +1709,34 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?team(COUNT(*) AS ?count) WHERE {
+  VALUES ?event {
+    wd:Q1646964 wd:Q636022 wd:Q18076452 wd:Q106684402 wd:Q33112992
+  }
+  VALUES ?team {
+    wd:Q1513127 wd:Q586949
+  }
+  ?event wdt:P1346 ?team
+}
+GROUP BY ?team</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00014.json</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
     </row>
     <row r="27" ht="65" customHeight="1">
       <c r="A27" s="6" t="n">
@@ -1467,19 +1759,30 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?club ?clubLabel WHERE {
+  wd:Q313446 wdt:P54 ?club .
+  ?club wdt:P17 wd:Q31 .
+  ?club rdfs:label ?clubLabel .
+  FILTER(LANG(?clubLabel) = 'en')
+}</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00308.json</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr"/>
       <c r="I27" s="7" t="inlineStr"/>
       <c r="J27" s="7" t="inlineStr"/>
       <c r="K27" s="7" t="inlineStr"/>
+      <c r="L27" s="7" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
     </row>
     <row r="28" ht="65" customHeight="1">
       <c r="A28" s="4" t="n">
@@ -1505,19 +1808,28 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?director ?location WHERE {
+  wd:Q186587 wdt:P57 ?director .
+  wd:Q186587 wdt:P915 ?location .
+}</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00305.json</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
       <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
     </row>
     <row r="29" ht="65" customHeight="1">
       <c r="A29" s="6" t="n">
@@ -1540,19 +1852,29 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?coach ?start ?end WHERE {
+  wd:Q167615 p:P286 ?statement .
+  ?statement ps:P286 ?coach ; pq:P580 ?start ; pq:P582 ?end .
+  FILTER(?start &lt;= "2012-11-03" ^^ xsd:date &amp;&amp; ?end &gt;= "2011-08-10" ^^ xsd:date)
+}</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00029.json</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr"/>
       <c r="I29" s="7" t="inlineStr"/>
       <c r="J29" s="7" t="inlineStr"/>
       <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
     </row>
     <row r="30" ht="65" customHeight="1">
       <c r="A30" s="4" t="n">
@@ -1575,19 +1897,35 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?country ?countryLabel ?population WHERE {
+  ?country wdt:P31 wd:Q3624078 .
+  ?country wdt:P30 wd:Q46 .
+  ?country wdt:P1082 ?population .
+  FILTER(?population &gt; 0)
+  .
+  ?country rdfs:label ?countryLabel .
+  FILTER(LANG(?countryLabel) = 'en')
+}
+ORDER BY ASC(?population)
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00440.json</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr"/>
       <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
     </row>
     <row r="31" ht="65" customHeight="1">
       <c r="A31" s="6" t="n">
@@ -1610,19 +1948,38 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?venue ?cityLabel ?stateLabel WHERE {
+  wd:Q199359 wdt:P131 ?city .
+  ?city rdfs:label ?cityLabel .
+  FILTER(LANG(?cityLabel) = 'en')
+  .
+  ?city wdt:P131 ?state .
+  ?state rdfs:label ?stateLabel .
+  FILTER(LANG(?stateLabel) = 'en')
+  .
+  wd:Q199359 rdfs:label ?venueLabel .
+  FILTER(LANG(?venueLabel) = 'en')
+  .
+  BIND("Camping World Stadium" AS ?venue)
+}</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr"/>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00963.json</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr"/>
       <c r="I31" s="7" t="inlineStr"/>
       <c r="J31" s="7" t="inlineStr"/>
       <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
     </row>
     <row r="32" ht="65" customHeight="1">
       <c r="A32" s="4" t="n">
@@ -1650,19 +2007,30 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?event ?eventLabel WHERE {
+  wd:Q34424 wdt:P793 ?event .
+  ?event rdfs:label ?eventLabel .
+  FILTER(LANG(?eventLabel) = 'en')
+}
+LIMIT 10</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00200.json</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr"/>
-      <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="5" t="inlineStr"/>
       <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
     </row>
     <row r="33" ht="65" customHeight="1">
       <c r="A33" s="6" t="n">
@@ -1685,19 +2053,28 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?start WHERE {
+  wd:Q11571 p:P54 ?membership .
+  ?membership ps:P54 wd:Q18656 ; pq:P580 ?start .
+}</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00058.json</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr"/>
       <c r="I33" s="7" t="inlineStr"/>
       <c r="J33" s="7" t="inlineStr"/>
       <c r="K33" s="7" t="inlineStr"/>
+      <c r="L33" s="7" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
     </row>
     <row r="34" ht="65" customHeight="1">
       <c r="A34" s="4" t="n">
@@ -1720,19 +2097,27 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?date WHERE {
+  wd:Q91805997 wdt:P577 ?date .
+}</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00128.json</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr"/>
-      <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr"/>
       <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr"/>
     </row>
     <row r="35" ht="65" customHeight="1">
       <c r="A35" s="6" t="n">
@@ -1755,19 +2140,35 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
+          <t>SELECT DISTINCT ?secretary ?label WHERE {
+  ?secretary p:P39 ?statement .
+  ?statement ps:P39 wd:Q642859 ; pq:P580 ?start ; pq:P582 ?end .
+  FILTER(xsd:dateTime(?start) &lt;= "2017-12-31T23:59:59Z" ^^ xsd:dateTime &amp;&amp; xsd:dateTime(?end) &gt;= "2017-01-01T00:00:00Z" ^^ xsd:dateTime)
+  .
+  OPTIONAL {
+    ?secretary rdfs:label ?label .
+    FILTER(LANG(?label) = "en")
+  }
+}
+ORDER BY ?start</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00099.json</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr"/>
-      <c r="H35" s="7" t="inlineStr"/>
       <c r="I35" s="7" t="inlineStr"/>
       <c r="J35" s="7" t="inlineStr"/>
       <c r="K35" s="7" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
     </row>
     <row r="36" ht="65" customHeight="1">
       <c r="A36" s="4" t="n">
@@ -1790,19 +2191,27 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?releaseDate WHERE {
+  wd:Q19938437 wdt:P577 ?releaseDate .
+}</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00131.json</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr"/>
-      <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="5" t="inlineStr"/>
       <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr"/>
+      <c r="M36" s="5" t="inlineStr"/>
     </row>
     <row r="37" ht="65" customHeight="1">
       <c r="A37" s="6" t="n">
@@ -1829,19 +2238,36 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?city ?cityLabel ?population WHERE {
+  ?city wdt:P31 wd:Q515 .
+  ?city wdt:P17 ?country .
+  ?country wdt:P30 wd:Q46 .
+  ?city wdt:P1082 ?population .
+  ?city rdfs:label ?cityLabel .
+  FILTER(lang(?cityLabel) = "en")
+  .
+  FILTER(isNumeric(?population))
+}
+ORDER BY DESC(?population)
+LIMIT 5</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00361.json</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="7" t="inlineStr"/>
       <c r="J37" s="7" t="inlineStr"/>
       <c r="K37" s="7" t="inlineStr"/>
+      <c r="L37" s="7" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
     </row>
     <row r="38" ht="65" customHeight="1">
       <c r="A38" s="4" t="n">
@@ -1866,19 +2292,38 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?team ?teamLabel(COUNT(?final) AS ?appearances) WHERE {
+  VALUES ?team {
+    wd:Q249679 wd:Q2521385 wd:Q2272176
+  }
+  {
+    ?final wdt:P2715 ?team
+  } UNION {
+    ?final wdt:P1346 ?team
+  }
+  ?team rdfs:label ?teamLabel .
+  FILTER(LANG(?teamLabel) = "en")
+}
+GROUP BY ?team ?teamLabel
+ORDER BY DESC(?appearances)</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00042.json</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="5" t="inlineStr"/>
       <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="5" t="inlineStr"/>
+      <c r="M38" s="5" t="inlineStr"/>
     </row>
     <row r="39" ht="65" customHeight="1">
       <c r="A39" s="6" t="n">
@@ -1901,19 +2346,27 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?country WHERE {
+  wd:Q142794 wdt:P27 ?country .
+}</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr"/>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00156.json</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr"/>
-      <c r="H39" s="7" t="inlineStr"/>
       <c r="I39" s="7" t="inlineStr"/>
       <c r="J39" s="7" t="inlineStr"/>
       <c r="K39" s="7" t="inlineStr"/>
+      <c r="L39" s="7" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
     </row>
     <row r="40" ht="65" customHeight="1">
       <c r="A40" s="4" t="n">
@@ -1936,19 +2389,33 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(DISTINCT ?artist) AS ?count) WHERE {
+  ?song wdt:P31 / wdt:P279 * wd:Q7366 ; wdt:P1344 / wdt:P361 wd:Q123894 ; wdt:P1344 / wdt:P2414 wd:Q5959621 ; wdt:P162 ?producer ; wdt:P175 ?artist .
+  ?producer rdfs:label ?producerLabel .
+  ?artist wdt:P1411 wd:Q1106130 .
+  FILTER REGEX(?producerLabel , "palmisano|palmasi" , "i")
+  .
+  FILTER(LANG(?producerLabel) = "it")
+  .
+}</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/OTT_QA_dev_complex/00061.json</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="5" t="inlineStr"/>
       <c r="K40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="inlineStr"/>
+      <c r="M40" s="5" t="inlineStr"/>
     </row>
     <row r="41" ht="65" customHeight="1">
       <c r="A41" s="6" t="n">
@@ -1971,19 +2438,28 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(?season) AS ?count) WHERE {
+  ?season wdt:P3450 wd:Q27192 .
+  ?season wdt:P1346 wd:Q620722 .
+}</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00175.json</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr"/>
-      <c r="H41" s="7" t="inlineStr"/>
       <c r="I41" s="7" t="inlineStr"/>
       <c r="J41" s="7" t="inlineStr"/>
       <c r="K41" s="7" t="inlineStr"/>
+      <c r="L41" s="7" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
     </row>
     <row r="42" ht="65" customHeight="1">
       <c r="A42" s="4" t="n">
@@ -2007,19 +2483,28 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?partner WHERE {
+  wd:Q7381061 wdt:P1327 ?partner .
+  ?partner wdt:P21 wd:Q6581072
+}</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/OTT_QA_dev_complex/00320.json</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr"/>
-      <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="5" t="inlineStr"/>
       <c r="K42" s="5" t="inlineStr"/>
+      <c r="L42" s="5" t="inlineStr"/>
+      <c r="M42" s="5" t="inlineStr"/>
     </row>
     <row r="43" ht="65" customHeight="1">
       <c r="A43" s="6" t="n">
@@ -2046,19 +2531,35 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
+          <t>SELECT DISTINCT ?building ?height ?buildingLabel WHERE {
+  ?building wdt:P31 / wdt:P279 * wd:Q41176 .
+  ?building wdt:P2048 ?height .
+  FILTER(xsd:double(?height) &gt; 350)
+  OPTIONAL {
+    ?building rdfs:label ?buildingLabel .
+    FILTER(LANG(?buildingLabel) = "en")
+  }
+}
+ORDER BY DESC(xsd:double(?height))
+LIMIT 5</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr"/>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00042.json</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr"/>
-      <c r="H43" s="7" t="inlineStr"/>
       <c r="I43" s="7" t="inlineStr"/>
       <c r="J43" s="7" t="inlineStr"/>
       <c r="K43" s="7" t="inlineStr"/>
+      <c r="L43" s="7" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
     </row>
     <row r="44" ht="65" customHeight="1">
       <c r="A44" s="4" t="n">
@@ -2081,19 +2582,28 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(?work) AS ?count) WHERE {
+  ?work wdt:P50 wd:Q209641 ; wdt:P123 wd:Q2335880 ; wdt:P577 ?date ; wdt:P31 wd:Q82622 .
+  FILTER(year(?date) &gt; 1963)
+}</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00008.json</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr"/>
-      <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="5" t="inlineStr"/>
       <c r="K44" s="5" t="inlineStr"/>
+      <c r="L44" s="5" t="inlineStr"/>
+      <c r="M44" s="5" t="inlineStr"/>
     </row>
     <row r="45" ht="65" customHeight="1">
       <c r="A45" s="6" t="n">
@@ -2122,19 +2632,30 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?promotion ?label WHERE {
+  ?promotion wdt:P31 wd:Q721067 .
+  ?promotion wdt:P641 wd:Q11446353 .
+  ?promotion rdfs:label ?label .
+  FILTER(lang(?label) = "en")
+}</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr"/>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00043.json</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr"/>
-      <c r="H45" s="7" t="inlineStr"/>
       <c r="I45" s="7" t="inlineStr"/>
       <c r="J45" s="7" t="inlineStr"/>
       <c r="K45" s="7" t="inlineStr"/>
+      <c r="L45" s="7" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
     </row>
     <row r="46" ht="65" customHeight="1">
       <c r="A46" s="4" t="n">
@@ -2157,19 +2678,29 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(?match) AS ?appearances) WHERE {
+  wd:Q2458826 wdt:P1344 ?match .
+  ?match wdt:P585 ?date ; wdt:P710 wd:Q207894 .
+  FILTER(YEAR(?date) = 2011)
+}</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00009.json</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="5" t="inlineStr"/>
       <c r="K46" s="5" t="inlineStr"/>
+      <c r="L46" s="5" t="inlineStr"/>
+      <c r="M46" s="5" t="inlineStr"/>
     </row>
     <row r="47" ht="65" customHeight="1">
       <c r="A47" s="6" t="n">
@@ -2192,19 +2723,27 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(*) AS ?count) WHERE {
+  ?season wdt:P31 / wdt:P279 * wd:Q2020029 ; wdt:P361 / wdt:P279 * wd:Q188482 ; wdt:P1346 wd:Q814738 .
+}</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr"/>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="H47" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/OTT_QA_dev_complex/00373.json</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr"/>
-      <c r="H47" s="7" t="inlineStr"/>
       <c r="I47" s="7" t="inlineStr"/>
       <c r="J47" s="7" t="inlineStr"/>
       <c r="K47" s="7" t="inlineStr"/>
+      <c r="L47" s="7" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr"/>
     </row>
     <row r="48" ht="65" customHeight="1">
       <c r="A48" s="4" t="n">
@@ -2227,19 +2766,31 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(*) AS ?count) WHERE {
+  ?event wdt:P361 wd:Q8411 ; wdt:P2094 wd:Q18345817 ; wdt:P276 wd:Q330136 .
+  ?venue wdt:P1533 ?fireEvent .
+  ?fireEvent wdt:P585 ?date .
+  FILTER(YEAR(?date) = 1991)
+  .
+}</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/OTT_QA_dev_complex/00217.json</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="5" t="inlineStr"/>
       <c r="K48" s="5" t="inlineStr"/>
+      <c r="L48" s="5" t="inlineStr"/>
+      <c r="M48" s="5" t="inlineStr"/>
     </row>
     <row r="49" ht="65" customHeight="1">
       <c r="A49" s="6" t="n">
@@ -2262,19 +2813,29 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(*) AS ?count) WHERE {
+  wd:Q276815 wdt:P1355 ?wins ; wdt:P1356 ?losses
+  FILTER(?losses &gt; 100)
+  .
+}</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr"/>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/OTT_QA_dev_complex/00334.json</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr"/>
-      <c r="H49" s="7" t="inlineStr"/>
       <c r="I49" s="7" t="inlineStr"/>
       <c r="J49" s="7" t="inlineStr"/>
       <c r="K49" s="7" t="inlineStr"/>
+      <c r="L49" s="7" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
     </row>
     <row r="50" ht="65" customHeight="1">
       <c r="A50" s="4" t="n">
@@ -2297,19 +2858,29 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?award ?awardLabel WHERE {
+  wd:Q2268391 wdt:P166 ?award .
+  ?award rdfs:label ?awardLabel .
+  FILTER(LANG(?awardLabel) = "en")
+}</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00057.json</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr"/>
-      <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="5" t="inlineStr"/>
       <c r="K50" s="5" t="inlineStr"/>
+      <c r="L50" s="5" t="inlineStr"/>
+      <c r="M50" s="5" t="inlineStr"/>
     </row>
     <row r="51" ht="65" customHeight="1">
       <c r="A51" s="6" t="n">
@@ -2332,19 +2903,30 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(DISTINCT ?game) AS ?count) WHERE {
+  VALUES ?series {
+    wd:Q56692089 wd:Q14870260 wd:Q3511178
+  }
+  ?game wdt:P361 ?series ; wdt:P276 wd:Q49136 ; wdt:P1923 wd:Q213959 .
+}</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr"/>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00070.json</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr"/>
-      <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr"/>
       <c r="J51" s="7" t="inlineStr"/>
       <c r="K51" s="7" t="inlineStr"/>
+      <c r="L51" s="7" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
     </row>
     <row r="52" ht="65" customHeight="1">
       <c r="A52" s="4" t="n">
@@ -2367,19 +2949,29 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(?game) AS ?count) WHERE {
+  ?series wdt:P31 wd:Q1363275 .
+  ?game wdt:P361 ?series ; wdt:P710 wd:Q334634 ; wdt:P710 wd:Q650840 ; wdt:P2003 ?homeScore ; wdt:P2004 ?awayScore .
+  FILTER(xsd:integer(?homeScore) + xsd:integer(?awayScore) &gt; 10)
+}</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00145.json</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr"/>
-      <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="5" t="inlineStr"/>
       <c r="K52" s="5" t="inlineStr"/>
+      <c r="L52" s="5" t="inlineStr"/>
+      <c r="M52" s="5" t="inlineStr"/>
     </row>
     <row r="53" ht="65" customHeight="1">
       <c r="A53" s="6" t="n">
@@ -2402,19 +2994,37 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(?game) AS ?count) WHERE {
+  VALUES ?year {
+    1977 1978 2008 2009
+  }
+  wd:Q334634 wdt:P1344 ?series .
+  wd:Q650840 wdt:P1344 ?series .
+  ?series wdt:P585 ?date .
+  BIND(YEAR(?date) AS ?yearFiltered)
+  FILTER(?yearFiltered = ?year)
+  ?game wdt:P361 ?series .
+  ?game wdt:P1110 ?attendance .
+  FILTER(STRDT(STRBEFORE(?attendance , '.') , xsd:integer) &gt; 50000)
+}</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr"/>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00088.json</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr"/>
-      <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr"/>
       <c r="J53" s="7" t="inlineStr"/>
       <c r="K53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
     </row>
     <row r="54" ht="65" customHeight="1">
       <c r="A54" s="4" t="n">
@@ -2438,19 +3048,33 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?team ?teamLabel WHERE {
+  wd:Q21621995 p:P54 ?statement .
+  ?statement ps:P54 ?team .
+  FILTER NOT EXISTS {
+    ?statement pq:P582 ?endTime .
+  }
+  ?team rdfs:label ?teamLabel .
+  FILTER(LANG(?teamLabel) = "en")
+}</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="H54" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00077.json</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="5" t="inlineStr"/>
       <c r="K54" s="5" t="inlineStr"/>
+      <c r="L54" s="5" t="inlineStr"/>
+      <c r="M54" s="5" t="inlineStr"/>
     </row>
     <row r="55" ht="65" customHeight="1">
       <c r="A55" s="6" t="n">
@@ -2473,19 +3097,32 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(?game) AS ?total) WHERE {
+  VALUES ?series {
+    wd:Q56692089 wd:Q14870260 wd:Q3511178
+  }
+  ?series wdt:P580 ?seriesStart ; wdt:P582 ?seriesEnd .
+  ?game wdt:P31 wd:Q200199 ; wdt:P276 wd:Q49136 ; wdt:P585 ?gameTime .
+  FILTER(?gameTime &gt;= ?seriesStart &amp;&amp; ?gameTime &lt;= ?seriesEnd)
+}</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr"/>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00150.json</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr"/>
-      <c r="H55" s="7" t="inlineStr"/>
       <c r="I55" s="7" t="inlineStr"/>
       <c r="J55" s="7" t="inlineStr"/>
       <c r="K55" s="7" t="inlineStr"/>
+      <c r="L55" s="7" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
     </row>
     <row r="56" ht="65" customHeight="1">
       <c r="A56" s="4" t="n">
@@ -2508,19 +3145,32 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?character ?label WHERE {
+  wd:Q35085291 wdt:P144 ?manga .
+  ?manga wdt:P674 ?character .
+  ?character wdt:P31 / wdt:P279 * wd:Q95074 .
+  ?character rdfs:label ?label .
+  FILTER(LANG(?label) = "en")
+}
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="H56" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00205.json</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr"/>
-      <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="5" t="inlineStr"/>
       <c r="K56" s="5" t="inlineStr"/>
+      <c r="L56" s="5" t="inlineStr"/>
+      <c r="M56" s="5" t="inlineStr"/>
     </row>
     <row r="57" ht="65" customHeight="1">
       <c r="A57" s="6" t="n">
@@ -2543,19 +3193,30 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
+          <t>SELECT(SUM(?games) AS ?totalGames) WHERE {
+  VALUES ?series {
+    wd:Q3511178 wd:Q14870260 wd:Q56692089
+  }
+  ?series wdt:P1500 ?games .
+}</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr"/>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00141.json</t>
         </is>
       </c>
-      <c r="G57" s="7" t="inlineStr"/>
-      <c r="H57" s="7" t="inlineStr"/>
       <c r="I57" s="7" t="inlineStr"/>
       <c r="J57" s="7" t="inlineStr"/>
       <c r="K57" s="7" t="inlineStr"/>
+      <c r="L57" s="7" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr"/>
     </row>
     <row r="58" ht="65" customHeight="1">
       <c r="A58" s="4" t="n">
@@ -2578,19 +3239,34 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?album ?albumLabel WHERE {
+  ?album wdt:P175 wd:Q1299 ; wdt:P577 ?date .
+  ?album rdfs:label ?albumLabel .
+  FILTER(LANG(?albumLabel) = "en")
+  .
+  FILTER(?date &lt; "1971-01-01" ^^ xsd:date)
+  .
+}
+ORDER BY DESC(?date)
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="H58" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00196.json</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr"/>
-      <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="5" t="inlineStr"/>
       <c r="K58" s="5" t="inlineStr"/>
+      <c r="L58" s="5" t="inlineStr"/>
+      <c r="M58" s="5" t="inlineStr"/>
     </row>
     <row r="59" ht="65" customHeight="1">
       <c r="A59" s="6" t="n">
@@ -2617,19 +3293,30 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?game ?label WHERE {
+  ?game wdt:P31 wd:Q438419 .
+  ?game rdfs:label ?label .
+  FILTER(LANG(?label) = "en")
+}
+LIMIT 5</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr"/>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr">
+      <c r="H59" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00026.json</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr"/>
-      <c r="H59" s="7" t="inlineStr"/>
       <c r="I59" s="7" t="inlineStr"/>
       <c r="J59" s="7" t="inlineStr"/>
       <c r="K59" s="7" t="inlineStr"/>
+      <c r="L59" s="7" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
     </row>
     <row r="60" ht="65" customHeight="1">
       <c r="A60" s="4" t="n">
@@ -2652,19 +3339,32 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?movie ?movieLabel WHERE {
+  ?movie wdt:P57 ?producer .
+  ?producer p:P166 ?award .
+  ?award ps:P166 wd:Q102427 ; pq:P585 "2021-04-25T00:00:00Z" ^^ xsd:dateTime .
+  ?movie rdfs:label ?movieLabel .
+  FILTER(LANG(?movieLabel) = "en")
+}
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00236.json</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr"/>
-      <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="5" t="inlineStr"/>
       <c r="K60" s="5" t="inlineStr"/>
+      <c r="L60" s="5" t="inlineStr"/>
+      <c r="M60" s="5" t="inlineStr"/>
     </row>
     <row r="61" ht="65" customHeight="1">
       <c r="A61" s="6" t="n">
@@ -2687,19 +3387,30 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(*) AS ?goldCount) WHERE {
+  ?athlete wdt:P27 wd:Q794 .
+  ?athlete p:P1344 ?participation .
+  ?participation ps:P1344 wd:Q729664 .
+  ?participation pq:P1346 wd:Q190546 .
+}</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr"/>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr">
+      <c r="H61" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/OTT_QA_dev_complex/00188.json</t>
         </is>
       </c>
-      <c r="G61" s="7" t="inlineStr"/>
-      <c r="H61" s="7" t="inlineStr"/>
       <c r="I61" s="7" t="inlineStr"/>
       <c r="J61" s="7" t="inlineStr"/>
       <c r="K61" s="7" t="inlineStr"/>
+      <c r="L61" s="7" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
     </row>
     <row r="62" ht="65" customHeight="1">
       <c r="A62" s="4" t="n">
@@ -2724,19 +3435,29 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?weapon ?weaponLabel WHERE {
+  ?weapon wdt:P31 wd:Q183302 .
+  ?weapon rdfs:label ?weaponLabel .
+  FILTER(LANG(?weaponLabel) = "en")
+}</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="H62" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00017.json</t>
         </is>
       </c>
-      <c r="G62" s="5" t="inlineStr"/>
-      <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="5" t="inlineStr"/>
       <c r="K62" s="5" t="inlineStr"/>
+      <c r="L62" s="5" t="inlineStr"/>
+      <c r="M62" s="5" t="inlineStr"/>
     </row>
     <row r="63" ht="65" customHeight="1">
       <c r="A63" s="6" t="n">
@@ -2759,19 +3480,29 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(?match) AS ?count) WHERE {
+  wd:Q2058682 wdt:P1344 ?match .
+  ?match wdt:P31 wd:Q26192625 ; wdt:P710 wd:Q172221 ; wdt:P585 ?date .
+  FILTER(YEAR(?date) = 2014)
+}</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr"/>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr">
+      <c r="H63" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00129.json</t>
         </is>
       </c>
-      <c r="G63" s="7" t="inlineStr"/>
-      <c r="H63" s="7" t="inlineStr"/>
       <c r="I63" s="7" t="inlineStr"/>
       <c r="J63" s="7" t="inlineStr"/>
       <c r="K63" s="7" t="inlineStr"/>
+      <c r="L63" s="7" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr"/>
     </row>
     <row r="64" ht="65" customHeight="1">
       <c r="A64" s="4" t="n">
@@ -2794,19 +3525,30 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(DISTINCT ?movie) AS ?count) WHERE {
+  ?movie wdt:P179 wd:Q3627883 .
+  ?movie wdt:P31 / wdt:P279 * wd:Q11424 .
+  ?movie wdt:P577 ?releaseDate .
+  FILTER(YEAR(?releaseDate) &lt;= 2021)
+}</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00228.json</t>
         </is>
       </c>
-      <c r="G64" s="5" t="inlineStr"/>
-      <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="5" t="inlineStr"/>
       <c r="K64" s="5" t="inlineStr"/>
+      <c r="L64" s="5" t="inlineStr"/>
+      <c r="M64" s="5" t="inlineStr"/>
     </row>
     <row r="65" ht="65" customHeight="1">
       <c r="A65" s="6" t="n">
@@ -2829,19 +3571,28 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(DISTINCT ?runnerup) AS ?count) WHERE {
+  ?event wdt:P31 wd:Q19842146 ; wdt:P1346 wd:Q3044572 ; wdt:P1201 ?runnerup .
+  FILTER(?runnerup != wd:Q3044572)
+}</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr"/>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr">
+      <c r="H65" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00062.json</t>
         </is>
       </c>
-      <c r="G65" s="7" t="inlineStr"/>
-      <c r="H65" s="7" t="inlineStr"/>
       <c r="I65" s="7" t="inlineStr"/>
       <c r="J65" s="7" t="inlineStr"/>
       <c r="K65" s="7" t="inlineStr"/>
+      <c r="L65" s="7" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr"/>
     </row>
     <row r="66" ht="65" customHeight="1">
       <c r="A66" s="4" t="n">
@@ -2864,19 +3615,37 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?coach ?coachLabel WHERE {
+  wd:Q8682 p:P286 ?position .
+  ?position ps:P286 ?coach .
+  OPTIONAL {
+    ?position pq:P582 ?endTime .
+  }
+  FILTER(! BOUND(?endTime) || ?endTime &gt; NOW ())
+  .
+  OPTIONAL {
+    ?coach rdfs:label ?coachLabel .
+    FILTER(LANG(?coachLabel) = 'en')
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="H66" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00060.json</t>
         </is>
       </c>
-      <c r="G66" s="5" t="inlineStr"/>
-      <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="5" t="inlineStr"/>
       <c r="K66" s="5" t="inlineStr"/>
+      <c r="L66" s="5" t="inlineStr"/>
+      <c r="M66" s="5" t="inlineStr"/>
     </row>
     <row r="67" ht="65" customHeight="1">
       <c r="A67" s="6" t="n">
@@ -2899,19 +3668,30 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?album ?title WHERE {
+  ?album wdt:P175 wd:Q6174877 .
+  OPTIONAL {
+    ?album wdt:P1476 ?title
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr"/>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F67" s="6" t="inlineStr">
+      <c r="H67" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00236.json</t>
         </is>
       </c>
-      <c r="G67" s="7" t="inlineStr"/>
-      <c r="H67" s="7" t="inlineStr"/>
       <c r="I67" s="7" t="inlineStr"/>
       <c r="J67" s="7" t="inlineStr"/>
       <c r="K67" s="7" t="inlineStr"/>
+      <c r="L67" s="7" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr"/>
     </row>
     <row r="68" ht="65" customHeight="1">
       <c r="A68" s="4" t="n">
@@ -2934,19 +3714,27 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(?track) AS ?count) WHERE {
+  wd:Q1814801 wdt:P658 ?track .
+}</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="H68" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00258.json</t>
         </is>
       </c>
-      <c r="G68" s="5" t="inlineStr"/>
-      <c r="H68" s="5" t="inlineStr"/>
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="5" t="inlineStr"/>
       <c r="K68" s="5" t="inlineStr"/>
+      <c r="L68" s="5" t="inlineStr"/>
+      <c r="M68" s="5" t="inlineStr"/>
     </row>
     <row r="69" ht="65" customHeight="1">
       <c r="A69" s="6" t="n">
@@ -2969,19 +3757,29 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(DISTINCT ?state) AS ?count) WHERE {
+  wd:Q678233 wdt:P5325 ?station .
+  ?station wdt:P131 + ?state .
+  ?state wdt:P31 wd:Q35657 .
+}</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr"/>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr">
+      <c r="H69" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/OTT_QA_dev_complex/00390.json</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr"/>
-      <c r="H69" s="7" t="inlineStr"/>
       <c r="I69" s="7" t="inlineStr"/>
       <c r="J69" s="7" t="inlineStr"/>
       <c r="K69" s="7" t="inlineStr"/>
+      <c r="L69" s="7" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr"/>
     </row>
     <row r="70" ht="65" customHeight="1">
       <c r="A70" s="4" t="n">
@@ -3004,19 +3802,27 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?count WHERE {
+  wd:Q308822 wdt:P1132 ?count .
+}</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr"/>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="H70" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00185.json</t>
         </is>
       </c>
-      <c r="G70" s="5" t="inlineStr"/>
-      <c r="H70" s="5" t="inlineStr"/>
       <c r="I70" s="5" t="inlineStr"/>
       <c r="J70" s="5" t="inlineStr"/>
       <c r="K70" s="5" t="inlineStr"/>
+      <c r="L70" s="5" t="inlineStr"/>
+      <c r="M70" s="5" t="inlineStr"/>
     </row>
     <row r="71" ht="65" customHeight="1">
       <c r="A71" s="6" t="n">
@@ -3039,19 +3845,33 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?player ?playerLabel ?goals WHERE {
+  ?player p:P54 ?membership .
+  ?membership ps:P54 wd:Q41420 .
+  ?membership pq:P1351 ?goals .
+  ?player rdfs:label ?playerLabel .
+  FILTER(lang(?playerLabel) = 'en')
+}
+ORDER BY DESC(xsd:integer(?goals))
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr"/>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="H71" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00220.json</t>
         </is>
       </c>
-      <c r="G71" s="7" t="inlineStr"/>
-      <c r="H71" s="7" t="inlineStr"/>
       <c r="I71" s="7" t="inlineStr"/>
       <c r="J71" s="7" t="inlineStr"/>
       <c r="K71" s="7" t="inlineStr"/>
+      <c r="L71" s="7" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr"/>
     </row>
     <row r="72" ht="65" customHeight="1">
       <c r="A72" s="4" t="n">
@@ -3074,19 +3894,30 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?player ?birthDate WHERE {
+  ?player wdt:P54 wd:Q43310 .
+  ?player wdt:P569 ?birthDate .
+}
+ORDER BY DESC(?birthDate)
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr">
+      <c r="H72" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00101.json</t>
         </is>
       </c>
-      <c r="G72" s="5" t="inlineStr"/>
-      <c r="H72" s="5" t="inlineStr"/>
       <c r="I72" s="5" t="inlineStr"/>
       <c r="J72" s="5" t="inlineStr"/>
       <c r="K72" s="5" t="inlineStr"/>
+      <c r="L72" s="5" t="inlineStr"/>
+      <c r="M72" s="5" t="inlineStr"/>
     </row>
     <row r="73" ht="65" customHeight="1">
       <c r="A73" s="6" t="n">
@@ -3109,19 +3940,32 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?year WHERE {
+  ?competition wdt:P1346 wd:Q958369 .
+  ?competition wdt:P585 ?date .
+  BIND(YEAR(?date) AS ?year)
+  FILTER(?year &gt;= 1988 &amp;&amp; ?year &lt;= 2013)
+}
+ORDER BY DESC(?year)
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr"/>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr">
+      <c r="H73" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/OTT_QA_dev_complex/00220.json</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr"/>
-      <c r="H73" s="7" t="inlineStr"/>
       <c r="I73" s="7" t="inlineStr"/>
       <c r="J73" s="7" t="inlineStr"/>
       <c r="K73" s="7" t="inlineStr"/>
+      <c r="L73" s="7" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
     </row>
     <row r="74" ht="65" customHeight="1">
       <c r="A74" s="4" t="n">
@@ -3144,19 +3988,29 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?year WHERE {
+  wd:Q260725 p:P166 ?stmt .
+  ?stmt ps:P166 wd:Q604370 ; pq:P585 ?date .
+  BIND(YEAR(?date) AS ?year)
+}</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr"/>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
+      <c r="H74" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00066.json</t>
         </is>
       </c>
-      <c r="G74" s="5" t="inlineStr"/>
-      <c r="H74" s="5" t="inlineStr"/>
       <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="5" t="inlineStr"/>
       <c r="K74" s="5" t="inlineStr"/>
+      <c r="L74" s="5" t="inlineStr"/>
+      <c r="M74" s="5" t="inlineStr"/>
     </row>
     <row r="75" ht="65" customHeight="1">
       <c r="A75" s="6" t="n">
@@ -3179,19 +4033,29 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
+          <t>SELECT(YEAR(?date) AS ?year) WHERE {
+  wd:Q26505 wdt:P571 ?date .
+}
+ORDER BY ASC(?date)
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr"/>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr">
+      <c r="H75" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00132.json</t>
         </is>
       </c>
-      <c r="G75" s="7" t="inlineStr"/>
-      <c r="H75" s="7" t="inlineStr"/>
       <c r="I75" s="7" t="inlineStr"/>
       <c r="J75" s="7" t="inlineStr"/>
       <c r="K75" s="7" t="inlineStr"/>
+      <c r="L75" s="7" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr"/>
     </row>
     <row r="76" ht="65" customHeight="1">
       <c r="A76" s="4" t="n">
@@ -3214,19 +4078,27 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
+          <t>SELECT(YEAR(?date) AS ?year) WHERE {
+  wd:Q191949 wdt:P577 ?date .
+}</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr"/>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="H76" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00147.json</t>
         </is>
       </c>
-      <c r="G76" s="5" t="inlineStr"/>
-      <c r="H76" s="5" t="inlineStr"/>
       <c r="I76" s="5" t="inlineStr"/>
       <c r="J76" s="5" t="inlineStr"/>
       <c r="K76" s="5" t="inlineStr"/>
+      <c r="L76" s="5" t="inlineStr"/>
+      <c r="M76" s="5" t="inlineStr"/>
     </row>
     <row r="77" ht="65" customHeight="1">
       <c r="A77" s="6" t="n">
@@ -3252,19 +4124,27 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?track WHERE {
+  wd:Q862386 wdt:P658 ?track
+}</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr"/>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F77" s="6" t="inlineStr">
+      <c r="H77" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00110.json</t>
         </is>
       </c>
-      <c r="G77" s="7" t="inlineStr"/>
-      <c r="H77" s="7" t="inlineStr"/>
       <c r="I77" s="7" t="inlineStr"/>
       <c r="J77" s="7" t="inlineStr"/>
       <c r="K77" s="7" t="inlineStr"/>
+      <c r="L77" s="7" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr"/>
     </row>
     <row r="78" ht="65" customHeight="1">
       <c r="A78" s="4" t="n">
@@ -3287,19 +4167,35 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(DISTINCT ?driver) AS ?count) WHERE {
+  {
+    ?team2002 wdt:P1344 wd:Q69844 .
+    ?team2002 wdt:P57 ?driver .
+  } UNION {
+    ?team2003 wdt:P1344 wd:Q69859 .
+    ?team2003 p:P57 ?stmt .
+    ?stmt ps:P57 ?driver .
+    ?stmt pq:P3831 wd:Q104121 .
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr"/>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="H78" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00180.json</t>
         </is>
       </c>
-      <c r="G78" s="5" t="inlineStr"/>
-      <c r="H78" s="5" t="inlineStr"/>
       <c r="I78" s="5" t="inlineStr"/>
       <c r="J78" s="5" t="inlineStr"/>
       <c r="K78" s="5" t="inlineStr"/>
+      <c r="L78" s="5" t="inlineStr"/>
+      <c r="M78" s="5" t="inlineStr"/>
     </row>
     <row r="79" ht="65" customHeight="1">
       <c r="A79" s="6" t="n">
@@ -3322,19 +4218,27 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?date WHERE {
+  wd:Q5435715 wdt:P577 ?date .
+}</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr"/>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
+      <c r="H79" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00011.json</t>
         </is>
       </c>
-      <c r="G79" s="7" t="inlineStr"/>
-      <c r="H79" s="7" t="inlineStr"/>
       <c r="I79" s="7" t="inlineStr"/>
       <c r="J79" s="7" t="inlineStr"/>
       <c r="K79" s="7" t="inlineStr"/>
+      <c r="L79" s="7" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr"/>
     </row>
     <row r="80" ht="65" customHeight="1">
       <c r="A80" s="4" t="n">
@@ -3357,19 +4261,28 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?year WHERE {
+  wd:Q289130 wdt:P577 ?date .
+  BIND(YEAR(?date) AS ?year)
+}</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="H80" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00016.json</t>
         </is>
       </c>
-      <c r="G80" s="5" t="inlineStr"/>
-      <c r="H80" s="5" t="inlineStr"/>
       <c r="I80" s="5" t="inlineStr"/>
       <c r="J80" s="5" t="inlineStr"/>
       <c r="K80" s="5" t="inlineStr"/>
+      <c r="L80" s="5" t="inlineStr"/>
+      <c r="M80" s="5" t="inlineStr"/>
     </row>
     <row r="81" ht="65" customHeight="1">
       <c r="A81" s="6" t="n">
@@ -3392,19 +4305,29 @@
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?date WHERE {
+  wd:Q1125262 p:P577 ?statement .
+  ?statement ps:P577 ?date .
+  ?statement pq:P291 wd:Q30 .
+}</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr"/>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
+      <c r="H81" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00128.json</t>
         </is>
       </c>
-      <c r="G81" s="7" t="inlineStr"/>
-      <c r="H81" s="7" t="inlineStr"/>
       <c r="I81" s="7" t="inlineStr"/>
       <c r="J81" s="7" t="inlineStr"/>
       <c r="K81" s="7" t="inlineStr"/>
+      <c r="L81" s="7" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr"/>
     </row>
     <row r="82" ht="65" customHeight="1">
       <c r="A82" s="4" t="n">
@@ -3427,19 +4350,31 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?time WHERE {
+  ?edition wdt:P3450 wd:Q178750 .
+  ?edition wdt:P1346 wd:Q83459 .
+  ?edition wdt:P585 ?time .
+}
+ORDER BY ?time
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr"/>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr">
+      <c r="H82" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00263.json</t>
         </is>
       </c>
-      <c r="G82" s="5" t="inlineStr"/>
-      <c r="H82" s="5" t="inlineStr"/>
       <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="5" t="inlineStr"/>
       <c r="K82" s="5" t="inlineStr"/>
+      <c r="L82" s="5" t="inlineStr"/>
+      <c r="M82" s="5" t="inlineStr"/>
     </row>
     <row r="83" ht="65" customHeight="1">
       <c r="A83" s="6" t="n">
@@ -3462,19 +4397,27 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?date WHERE {
+  wd:Q4922282 wdt:P577 ?date .
+}</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr"/>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F83" s="6" t="inlineStr">
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00023.json</t>
         </is>
       </c>
-      <c r="G83" s="7" t="inlineStr"/>
-      <c r="H83" s="7" t="inlineStr"/>
       <c r="I83" s="7" t="inlineStr"/>
       <c r="J83" s="7" t="inlineStr"/>
       <c r="K83" s="7" t="inlineStr"/>
+      <c r="L83" s="7" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr"/>
     </row>
     <row r="84" ht="65" customHeight="1">
       <c r="A84" s="4" t="n">
@@ -3500,19 +4443,32 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?award ?awardLabel ?date WHERE {
+  wd:Q2722967 p:P166 ?statement .
+  ?statement ps:P166 ?award .
+  ?award rdfs:label ?awardLabel .
+  FILTER(LANG(?awardLabel) = "en")
+  .
+  ?statement pq:P585 ?date .
+}</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="H84" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00192.json</t>
         </is>
       </c>
-      <c r="G84" s="5" t="inlineStr"/>
-      <c r="H84" s="5" t="inlineStr"/>
       <c r="I84" s="5" t="inlineStr"/>
       <c r="J84" s="5" t="inlineStr"/>
       <c r="K84" s="5" t="inlineStr"/>
+      <c r="L84" s="5" t="inlineStr"/>
+      <c r="M84" s="5" t="inlineStr"/>
     </row>
     <row r="85" ht="65" customHeight="1">
       <c r="A85" s="6" t="n">
@@ -3535,19 +4491,28 @@
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?year WHERE {
+  wd:Q367788 wdt:P571 ?foundingTime .
+  BIND(YEAR(?foundingTime) AS ?year)
+}</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr"/>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
+      <c r="H85" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/OTT_QA_dev_complex/00251.json</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr"/>
-      <c r="H85" s="7" t="inlineStr"/>
       <c r="I85" s="7" t="inlineStr"/>
       <c r="J85" s="7" t="inlineStr"/>
       <c r="K85" s="7" t="inlineStr"/>
+      <c r="L85" s="7" t="inlineStr"/>
+      <c r="M85" s="7" t="inlineStr"/>
     </row>
     <row r="86" ht="65" customHeight="1">
       <c r="A86" s="4" t="n">
@@ -3570,19 +4535,27 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?actor WHERE {
+  wd:Q4663084 wdt:P161 ?actor
+}</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr"/>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr">
+      <c r="H86" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00946.json</t>
         </is>
       </c>
-      <c r="G86" s="5" t="inlineStr"/>
-      <c r="H86" s="5" t="inlineStr"/>
       <c r="I86" s="5" t="inlineStr"/>
       <c r="J86" s="5" t="inlineStr"/>
       <c r="K86" s="5" t="inlineStr"/>
+      <c r="L86" s="5" t="inlineStr"/>
+      <c r="M86" s="5" t="inlineStr"/>
     </row>
     <row r="87" ht="65" customHeight="1">
       <c r="A87" s="6" t="n">
@@ -3605,19 +4578,28 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?label WHERE {
+  wd:Q3129199 rdfs:label ?label .
+  FILTER(LANG(?label) = "en")
+}</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr"/>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F87" s="6" t="inlineStr">
+      <c r="H87" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00482.json</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr"/>
-      <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="7" t="inlineStr"/>
       <c r="J87" s="7" t="inlineStr"/>
       <c r="K87" s="7" t="inlineStr"/>
+      <c r="L87" s="7" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr"/>
     </row>
     <row r="88" ht="65" customHeight="1">
       <c r="A88" s="4" t="n">
@@ -3640,19 +4622,27 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?capital WHERE {
+  wd:Q153136 wdt:P36 ?capital
+}</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr"/>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F88" s="4" t="inlineStr">
+      <c r="H88" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00636.json</t>
         </is>
       </c>
-      <c r="G88" s="5" t="inlineStr"/>
-      <c r="H88" s="5" t="inlineStr"/>
       <c r="I88" s="5" t="inlineStr"/>
       <c r="J88" s="5" t="inlineStr"/>
       <c r="K88" s="5" t="inlineStr"/>
+      <c r="L88" s="5" t="inlineStr"/>
+      <c r="M88" s="5" t="inlineStr"/>
     </row>
     <row r="89" ht="65" customHeight="1">
       <c r="A89" s="6" t="n">
@@ -3675,19 +4665,27 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?publicationDate WHERE {
+  wd:Q472208 wdt:P577 ?publicationDate .
+}</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr"/>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr">
+      <c r="H89" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00014.json</t>
         </is>
       </c>
-      <c r="G89" s="7" t="inlineStr"/>
-      <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="7" t="inlineStr"/>
       <c r="J89" s="7" t="inlineStr"/>
       <c r="K89" s="7" t="inlineStr"/>
+      <c r="L89" s="7" t="inlineStr"/>
+      <c r="M89" s="7" t="inlineStr"/>
     </row>
     <row r="90" ht="65" customHeight="1">
       <c r="A90" s="4" t="n">
@@ -3710,19 +4708,27 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?date WHERE {
+  wd:Q182502 wdt:P577 ?date .
+}</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr"/>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr">
+      <c r="H90" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00109.json</t>
         </is>
       </c>
-      <c r="G90" s="5" t="inlineStr"/>
-      <c r="H90" s="5" t="inlineStr"/>
       <c r="I90" s="5" t="inlineStr"/>
       <c r="J90" s="5" t="inlineStr"/>
       <c r="K90" s="5" t="inlineStr"/>
+      <c r="L90" s="5" t="inlineStr"/>
+      <c r="M90" s="5" t="inlineStr"/>
     </row>
     <row r="91" ht="65" customHeight="1">
       <c r="A91" s="6" t="n">
@@ -3745,19 +4751,27 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?date WHERE {
+  wd:Q7784391 wdt:P577 ?date
+}</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr"/>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F91" s="6" t="inlineStr">
+      <c r="H91" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00382.json</t>
         </is>
       </c>
-      <c r="G91" s="7" t="inlineStr"/>
-      <c r="H91" s="7" t="inlineStr"/>
       <c r="I91" s="7" t="inlineStr"/>
       <c r="J91" s="7" t="inlineStr"/>
       <c r="K91" s="7" t="inlineStr"/>
+      <c r="L91" s="7" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr"/>
     </row>
     <row r="92" ht="65" customHeight="1">
       <c r="A92" s="4" t="n">
@@ -3780,19 +4794,27 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?date WHERE {
+  wd:Q2574754 wdt:P577 ?date .
+}</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr"/>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F92" s="4" t="inlineStr">
+      <c r="H92" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00087.json</t>
         </is>
       </c>
-      <c r="G92" s="5" t="inlineStr"/>
-      <c r="H92" s="5" t="inlineStr"/>
       <c r="I92" s="5" t="inlineStr"/>
       <c r="J92" s="5" t="inlineStr"/>
       <c r="K92" s="5" t="inlineStr"/>
+      <c r="L92" s="5" t="inlineStr"/>
+      <c r="M92" s="5" t="inlineStr"/>
     </row>
     <row r="93" ht="65" customHeight="1">
       <c r="A93" s="6" t="n">
@@ -3815,19 +4837,27 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?author WHERE {
+  wd:Q1360987 wdt:P50 ?author
+}</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr"/>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F93" s="6" t="inlineStr">
+      <c r="H93" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00797.json</t>
         </is>
       </c>
-      <c r="G93" s="7" t="inlineStr"/>
-      <c r="H93" s="7" t="inlineStr"/>
       <c r="I93" s="7" t="inlineStr"/>
       <c r="J93" s="7" t="inlineStr"/>
       <c r="K93" s="7" t="inlineStr"/>
+      <c r="L93" s="7" t="inlineStr"/>
+      <c r="M93" s="7" t="inlineStr"/>
     </row>
     <row r="94" ht="65" customHeight="1">
       <c r="A94" s="4" t="n">
@@ -3850,19 +4880,32 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?location ?locationLabel WHERE {
+  ?location wdt:P31 wd:Q494978 .
+  ?location wdt:P17 wd:Q212 .
+  OPTIONAL {
+    ?location rdfs:label ?locationLabel
+    FILTER(lang(?locationLabel) = 'en')
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F94" s="4" t="inlineStr">
+      <c r="H94" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00047.json</t>
         </is>
       </c>
-      <c r="G94" s="5" t="inlineStr"/>
-      <c r="H94" s="5" t="inlineStr"/>
       <c r="I94" s="5" t="inlineStr"/>
       <c r="J94" s="5" t="inlineStr"/>
       <c r="K94" s="5" t="inlineStr"/>
+      <c r="L94" s="5" t="inlineStr"/>
+      <c r="M94" s="5" t="inlineStr"/>
     </row>
     <row r="95" ht="65" customHeight="1">
       <c r="A95" s="6" t="n">
@@ -3885,19 +4928,27 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?winner WHERE {
+  wd:Q47295100 wdt:P1346 ?winner .
+}</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr"/>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F95" s="6" t="inlineStr">
+      <c r="H95" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00362.json</t>
         </is>
       </c>
-      <c r="G95" s="7" t="inlineStr"/>
-      <c r="H95" s="7" t="inlineStr"/>
       <c r="I95" s="7" t="inlineStr"/>
       <c r="J95" s="7" t="inlineStr"/>
       <c r="K95" s="7" t="inlineStr"/>
+      <c r="L95" s="7" t="inlineStr"/>
+      <c r="M95" s="7" t="inlineStr"/>
     </row>
     <row r="96" ht="65" customHeight="1">
       <c r="A96" s="4" t="n">
@@ -3920,19 +4971,27 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?spouse WHERE {
+  wd:Q34743 wdt:P26 ?spouse
+}</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F96" s="4" t="inlineStr">
+      <c r="H96" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00235.json</t>
         </is>
       </c>
-      <c r="G96" s="5" t="inlineStr"/>
-      <c r="H96" s="5" t="inlineStr"/>
       <c r="I96" s="5" t="inlineStr"/>
       <c r="J96" s="5" t="inlineStr"/>
       <c r="K96" s="5" t="inlineStr"/>
+      <c r="L96" s="5" t="inlineStr"/>
+      <c r="M96" s="5" t="inlineStr"/>
     </row>
     <row r="97" ht="65" customHeight="1">
       <c r="A97" s="6" t="n">
@@ -3951,19 +5010,31 @@
       <c r="D97" s="6" t="inlineStr"/>
       <c r="E97" s="6" t="inlineStr">
         <is>
+          <t>SELECT((MAX(YEAR(?date)) - MIN(YEAR(?date))) AS ?difference) WHERE {
+  {
+    ?edition wdt:P1346 wd:Q334634 ; wdt:P1344 wd:Q650840 ; wdt:P585 ?date
+  } UNION {
+    ?edition wdt:P1346 wd:Q650840 ; wdt:P1344 wd:Q334634 ; wdt:P585 ?date
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr"/>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F97" s="6" t="inlineStr">
+      <c r="H97" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00198.json</t>
         </is>
       </c>
-      <c r="G97" s="7" t="inlineStr"/>
-      <c r="H97" s="7" t="inlineStr"/>
       <c r="I97" s="7" t="inlineStr"/>
       <c r="J97" s="7" t="inlineStr"/>
       <c r="K97" s="7" t="inlineStr"/>
+      <c r="L97" s="7" t="inlineStr"/>
+      <c r="M97" s="7" t="inlineStr"/>
     </row>
     <row r="98" ht="65" customHeight="1">
       <c r="A98" s="4" t="n">
@@ -3982,19 +5053,33 @@
       <c r="D98" s="4" t="inlineStr"/>
       <c r="E98" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?title WHERE {
+  wd:Q63436583 wdt:P1113 ?numberOfEpisodes .
+  OPTIONAL {
+    ?episode wdt:P179 wd:Q63436583 ; wdt:P1545 '5' ; rdfs:label ?title .
+    FILTER(LANG(?title) = 'en')
+  }
+  FILTER(?numberOfEpisodes &gt;= 5)
+}
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr"/>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F98" s="4" t="inlineStr">
+      <c r="H98" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00537.json</t>
         </is>
       </c>
-      <c r="G98" s="5" t="inlineStr"/>
-      <c r="H98" s="5" t="inlineStr"/>
       <c r="I98" s="5" t="inlineStr"/>
       <c r="J98" s="5" t="inlineStr"/>
       <c r="K98" s="5" t="inlineStr"/>
+      <c r="L98" s="5" t="inlineStr"/>
+      <c r="M98" s="5" t="inlineStr"/>
     </row>
     <row r="99" ht="65" customHeight="1">
       <c r="A99" s="6" t="n">
@@ -4025,19 +5110,38 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?play ?playLabel ?film ?filmLabel(MIN(?release) AS ?earliestRelease) WHERE {
+  ?play wdt:P50 wd:Q315808 .
+  ?film wdt:P144 ?play ; wdt:P31 wd:Q11424 ; wdt:P577 ?release .
+  OPTIONAL {
+    ?play rdfs:label ?playLabel
+    FILTER(LANG(?playLabel) = "en")
+  }
+  OPTIONAL {
+    ?film rdfs:label ?filmLabel
+    FILTER(LANG(?filmLabel) = "en")
+  }
+}
+GROUP BY ?play ?playLabel ?film ?filmLabel
+ORDER BY ?earliestRelease</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr"/>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F99" s="6" t="inlineStr">
+      <c r="H99" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Monaco_non_time_complex/00057.json</t>
         </is>
       </c>
-      <c r="G99" s="7" t="inlineStr"/>
-      <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="7" t="inlineStr"/>
       <c r="J99" s="7" t="inlineStr"/>
       <c r="K99" s="7" t="inlineStr"/>
+      <c r="L99" s="7" t="inlineStr"/>
+      <c r="M99" s="7" t="inlineStr"/>
     </row>
     <row r="100" ht="65" customHeight="1">
       <c r="A100" s="4" t="n">
@@ -4060,27 +5164,37 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
+          <t>SELECT(xsd:integer(?matches) AS ?matches_count) WHERE {
+  wd:Q73360 p:P54 ?membership .
+  ?membership ps:P54 wd:Q166776 .
+  ?membership pq:P1350 ?matches .
+}</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr"/>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
           <t>Temporal changes</t>
         </is>
       </c>
-      <c r="F100" s="4" t="inlineStr">
+      <c r="H100" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00281.json</t>
         </is>
       </c>
-      <c r="G100" s="5" t="inlineStr"/>
-      <c r="H100" s="5" t="inlineStr"/>
       <c r="I100" s="5" t="inlineStr"/>
       <c r="J100" s="5" t="inlineStr"/>
       <c r="K100" s="5" t="inlineStr"/>
+      <c r="L100" s="5" t="inlineStr"/>
+      <c r="M100" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K100"/>
+  <autoFilter ref="A1:M100"/>
   <dataValidations count="2">
-    <dataValidation sqref="G2:G100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Correct,Incorrect,Unsure"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H100 I2:I100 J2:J100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J100 K2:K100 L2:L100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
